--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProjects\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2303DD3A-428C-41A9-B1EE-BFD514AEB4B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56208EDE-A2E3-4952-A93B-A022EF1D19D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="175">
   <si>
     <t>#</t>
   </si>
@@ -588,6 +588,10 @@
   </si>
   <si>
     <t>10000157;15@10000157;20@10000157;25@10000157;30@10000157;35@10000157;40</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>生活技能开启第二页需要充值数量(美元)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1018,7 +1022,7 @@
     <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="4" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="19.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.625" style="1" customWidth="1"/>
     <col min="5" max="5" width="57.375" style="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.5" style="4" customWidth="1"/>
@@ -2503,7 +2507,20 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C124" s="1">
+        <v>120</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E124" s="1">
+        <v>28</v>
+      </c>
+      <c r="F124" s="1">
+        <v>28</v>
+      </c>
+    </row>
     <row r="125" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProjects\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56208EDE-A2E3-4952-A93B-A022EF1D19D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC9F7D1-26AD-43B6-B0E4-BBB11DE83134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="174">
   <si>
     <t>#</t>
   </si>
@@ -588,10 +588,6 @@
   </si>
   <si>
     <t>10000157;15@10000157;20@10000157;25@10000157;30@10000157;35@10000157;40</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>生活技能开启第二页需要充值数量(美元)</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1016,7 +1012,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:H125"/>
+  <dimension ref="C1:H124"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
@@ -2507,21 +2503,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C124" s="1">
-        <v>120</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E124" s="1">
-        <v>28</v>
-      </c>
-      <c r="F124" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="125" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>

--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProjects\GitWeiJing\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC9F7D1-26AD-43B6-B0E4-BBB11DE83134}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7A9AD6-5BF3-453C-9C9B-A14FA184C433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
@@ -390,9 +390,6 @@
     <t>剧情副本怪物刷新</t>
   </si>
   <si>
-    <t>0.0065;6;100,80005001&amp;100,80005002&amp;100,80005003&amp;50,80005004&amp;50,80005005&amp;50,80005006&amp;50,80005007&amp;30,80005008&amp;30,80005009&amp;30,80005010&amp;30,80005011&amp;30,80005012&amp;30,80005013&amp;30,80005014@0.003;2;100,80006001&amp;100,80006002&amp;100,80006003&amp;80,80006004&amp;80,80006005&amp;80,80006006&amp;60,80006007&amp;60,80006008&amp;40,80006009&amp;40,80006010</t>
-  </si>
-  <si>
     <t>经验兑换道具</t>
   </si>
   <si>
@@ -588,6 +585,10 @@
   </si>
   <si>
     <t>10000157;15@10000157;20@10000157;25@10000157;30@10000157;35@10000157;40</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.0045;6;100,80005001&amp;100,80005002&amp;100,80005003&amp;50,80005004&amp;50,80005005&amp;50,80005006&amp;50,80005007&amp;30,80005008&amp;30,80005009&amp;30,80005010&amp;30,80005011&amp;30,80005012&amp;30,80005013&amp;30,80005014@0.003;2;100,80006001&amp;100,80006002&amp;100,80006003&amp;80,80006004&amp;80,80006005&amp;80,80006006&amp;60,80006007&amp;60,80006008&amp;40,80006009&amp;40,80006010</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1258,7 +1259,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>33</v>
@@ -1269,7 +1270,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E22" s="1">
         <v>880</v>
@@ -1456,7 +1457,7 @@
         <v>50</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="39" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1511,7 +1512,7 @@
         <v>56</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="44" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1547,7 +1548,7 @@
         <v>60</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="47" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -1639,7 +1640,7 @@
         <v>70</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="54" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2017,7 +2018,7 @@
         <v>114</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>115</v>
+        <v>173</v>
       </c>
     </row>
     <row r="85" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2025,7 +2026,7 @@
         <v>81</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E85" s="7">
         <v>60303101</v>
@@ -2036,10 +2037,10 @@
         <v>82</v>
       </c>
       <c r="D86" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E86" s="1" t="s">
         <v>117</v>
-      </c>
-      <c r="E86" s="1" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="87" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2047,10 +2048,10 @@
         <v>83</v>
       </c>
       <c r="D87" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E87" s="1" t="s">
         <v>119</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="88" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2058,7 +2059,7 @@
         <v>84</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E88" s="1">
         <v>10</v>
@@ -2072,7 +2073,7 @@
         <v>85</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E89" s="1">
         <v>10</v>
@@ -2086,10 +2087,10 @@
         <v>86</v>
       </c>
       <c r="D90" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E90" s="1" t="s">
         <v>123</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="91" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2097,10 +2098,10 @@
         <v>87</v>
       </c>
       <c r="D91" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E91" s="1" t="s">
         <v>125</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="92" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2108,10 +2109,10 @@
         <v>88</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="93" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2119,7 +2120,7 @@
         <v>89</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E93" s="1">
         <v>520</v>
@@ -2130,7 +2131,7 @@
         <v>90</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E94" s="1">
         <v>10000158</v>
@@ -2141,7 +2142,7 @@
         <v>91</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E95" s="1">
         <v>100</v>
@@ -2155,7 +2156,7 @@
         <v>24</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2163,7 +2164,7 @@
         <v>93</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E97" s="1">
         <v>30</v>
@@ -2177,7 +2178,7 @@
         <v>94</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E98" s="1">
         <v>200000</v>
@@ -2191,7 +2192,7 @@
         <v>95</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E99" s="1">
         <v>120</v>
@@ -2205,10 +2206,10 @@
         <v>96</v>
       </c>
       <c r="D100" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="101" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2216,10 +2217,10 @@
         <v>97</v>
       </c>
       <c r="D101" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E101" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="102" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2227,7 +2228,7 @@
         <v>98</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E102" s="1">
         <v>30000</v>
@@ -2241,7 +2242,7 @@
         <v>99</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E103" s="1">
         <v>61300001</v>
@@ -2255,10 +2256,10 @@
         <v>100</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2266,10 +2267,10 @@
         <v>101</v>
       </c>
       <c r="D105" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="E105" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="106" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2277,10 +2278,10 @@
         <v>102</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="107" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2288,7 +2289,7 @@
         <v>103</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E107" s="1">
         <v>70000001</v>
@@ -2302,7 +2303,7 @@
         <v>104</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E108" s="1">
         <v>300</v>
@@ -2313,7 +2314,7 @@
         <v>105</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E109" s="1">
         <v>30</v>
@@ -2327,7 +2328,7 @@
         <v>106</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E110" s="1">
         <v>80000001</v>
@@ -2341,10 +2342,10 @@
         <v>107</v>
       </c>
       <c r="D111" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="112" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2352,7 +2353,7 @@
         <v>108</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E112" s="1">
         <v>10</v>
@@ -2366,7 +2367,7 @@
         <v>109</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E113" s="1">
         <v>10</v>
@@ -2380,10 +2381,10 @@
         <v>110</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="115" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2391,10 +2392,10 @@
         <v>111</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2402,10 +2403,10 @@
         <v>112</v>
       </c>
       <c r="D116" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>158</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="117" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2413,7 +2414,7 @@
         <v>113</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E117" s="1">
         <v>198</v>
@@ -2427,7 +2428,7 @@
         <v>114</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E118" s="1">
         <v>90000001</v>
@@ -2441,7 +2442,7 @@
         <v>115</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E119" s="1">
         <v>120</v>
@@ -2455,10 +2456,10 @@
         <v>116</v>
       </c>
       <c r="D120" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E120" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="121" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -2466,7 +2467,7 @@
         <v>117</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E121" s="1">
         <v>6</v>
@@ -2480,7 +2481,7 @@
         <v>118</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E122" s="1">
         <v>50</v>
@@ -2494,7 +2495,7 @@
         <v>119</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E123" s="1">
         <v>60</v>

--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -1,37 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7A9AD6-5BF3-453C-9C9B-A14FA184C433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D84" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D84" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>刷新概率,每天刷新上限,刷新随机列表</t>
@@ -43,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="173">
   <si>
     <t>#</t>
   </si>
@@ -144,9 +150,15 @@
     <t>1;1000</t>
   </si>
   <si>
+    <t>兑换宠物道具消耗</t>
+  </si>
+  <si>
     <t>10010001;10</t>
   </si>
   <si>
+    <t>兑换宠物钻石消耗</t>
+  </si>
+  <si>
     <t>初始化学习制造列表</t>
   </si>
   <si>
@@ -198,6 +210,9 @@
     <t>宠物最大数量</t>
   </si>
   <si>
+    <t>1;5@25;6@35;7@45;8@55;9@65;10</t>
+  </si>
+  <si>
     <t>抽卡一次免费时间</t>
   </si>
   <si>
@@ -216,6 +231,9 @@
     <t>兑换宠物蛋一次消耗</t>
   </si>
   <si>
+    <t>3;150@601800041</t>
+  </si>
+  <si>
     <t>兑换宠物蛋十次消耗</t>
   </si>
   <si>
@@ -228,6 +246,9 @@
     <t>世界等级</t>
   </si>
   <si>
+    <t>1;25@2;29@3;35@4;39@5;45@6;49@7;54@8;56@9;58@10;65@11;70</t>
+  </si>
+  <si>
     <t>初始制造列表</t>
   </si>
   <si>
@@ -258,6 +279,9 @@
     <t>装备洗练度</t>
   </si>
   <si>
+    <t>2;7</t>
+  </si>
+  <si>
     <t>最大拍卖数量</t>
   </si>
   <si>
@@ -390,6 +414,9 @@
     <t>剧情副本怪物刷新</t>
   </si>
   <si>
+    <t>0.0045;6;100,80005001&amp;100,80005002&amp;100,80005003&amp;50,80005004&amp;50,80005005&amp;50,80005006&amp;50,80005007&amp;30,80005008&amp;30,80005009&amp;30,80005010&amp;30,80005011&amp;30,80005012&amp;30,80005013&amp;30,80005014@0.003;2;100,80006001&amp;100,80006002&amp;100,80006003&amp;80,80006004&amp;80,80006005&amp;80,80006006&amp;60,80006007&amp;60,80006008&amp;40,80006009&amp;40,80006010</t>
+  </si>
+  <si>
     <t>经验兑换道具</t>
   </si>
   <si>
@@ -426,6 +453,9 @@
     <t>传承道具消耗</t>
   </si>
   <si>
+    <t>10000157;15@10000157;20@10000157;25@10000157;30@10000157;35@10000157;40</t>
+  </si>
+  <si>
     <t>封印之塔消耗钻石</t>
   </si>
   <si>
@@ -490,113 +520,67 @@
   </si>
   <si>
     <t>宠物蛋抽奖折扣</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>300;0.8</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>家族每日次数</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>兑换宠物钻石消耗</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>兑换宠物道具消耗</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>周任务次数</t>
+  </si>
+  <si>
+    <t>兑换宠物之核一次消耗</t>
   </si>
   <si>
     <t>10000131;10@601800051</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>周任务次数</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>兑换宠物之核一次消耗</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>兑换宠物之核十次消耗</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000131;100@601800051</t>
   </si>
   <si>
     <t>宠物之核抽奖折扣</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>300;0.8</t>
   </si>
   <si>
     <t>生活技能开启第二页需要充值数量</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000131;100@601800051</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>活动1商店ID</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>3;150@601800041</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;5@25;6@35;7@45;8@55;9@65;10</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>账号仓库最大格子数量</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>2;7</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>洗练折扣</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>300;0.9</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>传承鉴定次数</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>宝石仓库格子数量</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>宠物背包数量</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>1;25@2;29@3;35@4;39@5;45@6;49@7;54@8;56@9;58@10;65@11;70</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>10000157;15@10000157;20@10000157;25@10000157;30@10000157;35@10000157;40</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.0045;6;100,80005001&amp;100,80005002&amp;100,80005003&amp;50,80005004&amp;50,80005005&amp;50,80005006&amp;50,80005007&amp;30,80005008&amp;30,80005009&amp;30,80005010&amp;30,80005011&amp;30,80005012&amp;30,80005013&amp;30,80005014@0.003;2;100,80006001&amp;100,80006002&amp;100,80006003&amp;80,80006004&amp;80,80006005&amp;80,80006006&amp;60,80006007&amp;60,80006008&amp;40,80006009&amp;40,80006010</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -608,7 +592,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -616,46 +599,172 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -668,8 +777,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -677,11 +972,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -703,24 +1240,65 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1007,14 +1585,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C1:H124"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="4" customWidth="1"/>
@@ -1027,13 +1605,13 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="20.1" customHeight="1"/>
+    <row r="2" ht="20.1" customHeight="1" spans="3:8">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="20.1" customHeight="1" spans="3:8">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1049,7 +1627,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="20.1" customHeight="1" spans="3:8">
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1063,7 +1641,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="20.1" customHeight="1" spans="3:8">
       <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1077,7 +1655,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1088,7 +1666,7 @@
         <v>30010000</v>
       </c>
     </row>
-    <row r="7" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1099,7 +1677,7 @@
         <v>60000011</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" ht="20.1" customHeight="1" spans="3:8">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1113,7 +1691,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" ht="20.1" customHeight="1" spans="3:8">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1127,18 +1705,18 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="8">
+    <row r="10" ht="20.1" customHeight="1" spans="3:8">
+      <c r="C10" s="7">
         <v>5</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" ht="20.1" customHeight="1" spans="3:8">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1149,29 +1727,29 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="8">
+    <row r="12" ht="20.1" customHeight="1" spans="3:8">
+      <c r="C12" s="7">
         <v>7</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="8">
+    <row r="13" ht="20.1" customHeight="1" spans="3:8">
+      <c r="C13" s="7">
         <v>8</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" ht="20.1" customHeight="1" spans="3:8">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1182,7 +1760,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" ht="20.1" customHeight="1" spans="3:8">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1196,7 +1774,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" ht="20.1" customHeight="1" spans="3:8">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1207,7 +1785,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" ht="20.1" customHeight="1" spans="3:6">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1221,7 +1799,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" ht="20.1" customHeight="1" spans="3:6">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1232,7 +1810,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" ht="20.1" customHeight="1" spans="3:6">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1243,7 +1821,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" ht="20.1" customHeight="1" spans="3:6">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1254,45 +1832,45 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" ht="20.1" customHeight="1" spans="3:6">
       <c r="C21" s="1">
         <v>16</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>152</v>
+        <v>33</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" ht="20.1" customHeight="1" spans="3:6">
       <c r="C22" s="1">
         <v>17</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="E22" s="1">
         <v>880</v>
       </c>
     </row>
-    <row r="23" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" ht="20.1" customHeight="1" spans="3:6">
       <c r="C23" s="1">
         <v>18</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E23" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C24" s="1">
         <v>19</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E24" s="1">
         <v>3</v>
@@ -1301,69 +1879,69 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" ht="20.1" customHeight="1" spans="3:6">
       <c r="C25" s="1">
         <v>20</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E25" s="1">
         <v>200000</v>
       </c>
     </row>
-    <row r="26" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" ht="20.1" customHeight="1" spans="3:6">
       <c r="C26" s="1">
         <v>21</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E26" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C27" s="1">
         <v>22</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E27" s="1">
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C28" s="1">
         <v>23</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E28" s="1">
         <v>50</v>
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C29" s="1">
         <v>24</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E29" s="1">
         <v>7</v>
       </c>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" ht="20.1" customHeight="1" spans="3:6">
       <c r="C30" s="1">
         <v>25</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E30" s="1">
         <v>5000</v>
@@ -1372,205 +1950,205 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="31" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" ht="20.1" customHeight="1" spans="3:6">
       <c r="C31" s="1">
         <v>26</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E31" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" ht="20.1" customHeight="1" spans="3:6">
       <c r="C32" s="1">
         <v>27</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E32" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" ht="20.1" customHeight="1" spans="3:7">
       <c r="C33" s="1">
         <v>28</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" ht="20.1" customHeight="1" spans="3:7">
       <c r="C34" s="1">
         <v>29</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E34" s="1">
         <v>1000</v>
       </c>
     </row>
-    <row r="35" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" ht="20.1" customHeight="1" spans="3:7">
       <c r="C35" s="1">
         <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E35" s="1">
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" ht="20.1" customHeight="1" spans="3:7">
       <c r="C36" s="1">
         <v>31</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E36" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" ht="20.1" customHeight="1" spans="3:7">
       <c r="C37" s="1">
         <v>33</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" ht="20.1" customHeight="1" spans="3:7">
       <c r="C38" s="1">
         <v>34</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="39" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" ht="20.1" customHeight="1" spans="3:7">
       <c r="C39" s="1">
         <v>35</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E39" s="1">
         <v>86400</v>
       </c>
     </row>
-    <row r="40" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" ht="20.1" customHeight="1" spans="3:7">
       <c r="C40" s="1">
         <v>36</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E40" s="1">
         <v>259200</v>
       </c>
     </row>
-    <row r="41" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" ht="20.1" customHeight="1" spans="3:7">
       <c r="C41" s="1">
         <v>37</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E41" s="1">
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" ht="20.1" customHeight="1" spans="3:7">
       <c r="C42" s="1">
         <v>38</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" ht="20.1" customHeight="1" spans="3:7">
       <c r="C43" s="1">
         <v>39</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="44" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="44" ht="20.1" customHeight="1" spans="3:7">
       <c r="C44" s="1">
         <v>40</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45" ht="20.1" customHeight="1" spans="3:7">
       <c r="C45" s="1">
         <v>41</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E45" s="1">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F45" s="1">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="46" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="46" ht="20.1" customHeight="1" spans="3:7">
       <c r="C46" s="1">
         <v>42</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="47" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" ht="20.1" customHeight="1" spans="3:7">
       <c r="C47" s="1">
         <v>43</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" ht="20.1" customHeight="1" spans="3:7">
       <c r="C48" s="1">
         <v>44</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="E48" s="1">
         <v>20</v>
@@ -1579,12 +2157,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" ht="20.1" customHeight="1" spans="3:6">
       <c r="C49" s="1">
         <v>45</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E49" s="1">
         <v>500</v>
@@ -1593,12 +2171,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" ht="20.1" customHeight="1" spans="3:6">
       <c r="C50" s="1">
         <v>46</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E50" s="1">
         <v>500</v>
@@ -1607,12 +2185,12 @@
         <v>500</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" ht="20.1" customHeight="1" spans="3:6">
       <c r="C51" s="1">
         <v>47</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E51" s="1">
         <v>101</v>
@@ -1621,34 +2199,34 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" ht="20.1" customHeight="1" spans="3:6">
       <c r="C52" s="1">
         <v>48</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="53" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="53" ht="20.1" customHeight="1" spans="3:6">
       <c r="C53" s="1">
         <v>49</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="54" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="54" ht="20.1" customHeight="1" spans="3:6">
       <c r="C54" s="1">
         <v>50</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="E54" s="1">
         <v>20</v>
@@ -1657,57 +2235,57 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" ht="20.1" customHeight="1" spans="3:6">
       <c r="C55" s="1">
         <v>51</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="56" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="56" ht="20.1" customHeight="1" spans="3:6">
       <c r="C56" s="1">
         <v>52</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" ht="20.1" customHeight="1" spans="3:6">
       <c r="C57" s="1">
         <v>53</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="58" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="58" ht="20.1" customHeight="1" spans="3:6">
       <c r="C58" s="1">
         <v>54</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="59" ht="20.1" customHeight="1" spans="3:6">
       <c r="C59" s="1">
         <v>55</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E59" s="1">
         <v>20000001</v>
@@ -1716,23 +2294,23 @@
         <v>20000001</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" ht="20.1" customHeight="1" spans="3:6">
       <c r="C60" s="1">
         <v>56</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="61" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="61" ht="20.1" customHeight="1" spans="3:6">
       <c r="C61" s="1">
         <v>57</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E61" s="1">
         <v>100</v>
@@ -1741,12 +2319,12 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" ht="20.1" customHeight="1" spans="3:6">
       <c r="C62" s="1">
         <v>58</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="E62" s="1">
         <v>10</v>
@@ -1755,12 +2333,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" ht="20.1" customHeight="1" spans="3:6">
       <c r="C63" s="1">
         <v>59</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E63" s="1">
         <v>30</v>
@@ -1769,12 +2347,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" ht="20.1" customHeight="1" spans="3:6">
       <c r="C64" s="1">
         <v>60</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E64" s="1">
         <v>60</v>
@@ -1783,45 +2361,45 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" ht="20.1" customHeight="1" spans="3:6">
       <c r="C65" s="1">
         <v>61</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="66" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="66" ht="20.1" customHeight="1" spans="3:6">
       <c r="C66" s="1">
         <v>62</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="67" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" ht="20.1" customHeight="1" spans="3:6">
       <c r="C67" s="1">
         <v>63</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="68" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="68" ht="20.1" customHeight="1" spans="3:6">
       <c r="C68" s="1">
         <v>64</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E68" s="1">
         <v>30000001</v>
@@ -1830,89 +2408,89 @@
         <v>30000001</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" ht="20.1" customHeight="1" spans="3:6">
       <c r="C69" s="1">
         <v>65</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="70" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" ht="20.1" customHeight="1" spans="3:6">
       <c r="C70" s="1">
         <v>66</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="71" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="71" ht="20.1" customHeight="1" spans="3:6">
       <c r="C71" s="1">
         <v>67</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="72" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" ht="20.1" customHeight="1" spans="3:6">
       <c r="C72" s="1">
         <v>68</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="E72" s="7">
+        <v>105</v>
+      </c>
+      <c r="E72" s="8">
         <v>60500101</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" ht="20.1" customHeight="1" spans="3:6">
       <c r="C73" s="1">
         <v>69</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E73" s="7">
+        <v>106</v>
+      </c>
+      <c r="E73" s="8">
         <v>60500201</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" ht="20.1" customHeight="1" spans="3:6">
       <c r="C74" s="1">
         <v>70</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="75" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="75" ht="20.1" customHeight="1" spans="3:6">
       <c r="C75" s="1">
         <v>71</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="76" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="76" ht="20.1" customHeight="1" spans="3:6">
       <c r="C76" s="1">
         <v>72</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E76" s="1">
         <v>180</v>
@@ -1921,12 +2499,12 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" ht="20.1" customHeight="1" spans="3:6">
       <c r="C77" s="1">
         <v>73</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E77" s="1">
         <v>880</v>
@@ -1935,12 +2513,12 @@
         <v>880</v>
       </c>
     </row>
-    <row r="78" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C78" s="1">
         <v>74</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E78" s="1">
         <v>3</v>
@@ -1949,23 +2527,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" ht="20.1" customHeight="1" spans="3:6">
       <c r="C79" s="1">
         <v>75</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E79" s="1">
         <v>601502001</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" ht="20.1" customHeight="1" spans="3:6">
       <c r="C80" s="1">
         <v>76</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E80" s="1">
         <v>40000001</v>
@@ -1974,23 +2552,23 @@
         <v>40000001</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" ht="20.1" customHeight="1" spans="3:6">
       <c r="C81" s="1">
         <v>77</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E81" s="1">
         <v>601503011</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" ht="20.1" customHeight="1" spans="3:6">
       <c r="C82" s="1">
         <v>78</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E82" s="1">
         <v>100</v>
@@ -1999,67 +2577,67 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" ht="20.1" customHeight="1" spans="3:6">
       <c r="C83" s="1">
         <v>79</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="84" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="84" ht="20.1" customHeight="1" spans="3:6">
       <c r="C84" s="1">
         <v>80</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="85" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="85" ht="20.1" customHeight="1" spans="3:6">
       <c r="C85" s="1">
         <v>81</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E85" s="7">
+        <v>122</v>
+      </c>
+      <c r="E85" s="8">
         <v>60303101</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" ht="20.1" customHeight="1" spans="3:6">
       <c r="C86" s="1">
         <v>82</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="87" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="87" ht="20.1" customHeight="1" spans="3:6">
       <c r="C87" s="1">
         <v>83</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="88" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="88" ht="20.1" customHeight="1" spans="3:6">
       <c r="C88" s="1">
         <v>84</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E88" s="1">
         <v>10</v>
@@ -2068,12 +2646,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" ht="20.1" customHeight="1" spans="3:6">
       <c r="C89" s="1">
         <v>85</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E89" s="1">
         <v>10</v>
@@ -2082,73 +2660,73 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" ht="20.1" customHeight="1" spans="3:6">
       <c r="C90" s="1">
         <v>86</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="91" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="91" ht="20.1" customHeight="1" spans="3:6">
       <c r="C91" s="1">
         <v>87</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="92" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="92" ht="20.1" customHeight="1" spans="3:6">
       <c r="C92" s="1">
         <v>88</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="93" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="93" ht="20.1" customHeight="1" spans="3:6">
       <c r="C93" s="1">
         <v>89</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="E93" s="1">
         <v>520</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" ht="20.1" customHeight="1" spans="3:6">
       <c r="C94" s="1">
         <v>90</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="E94" s="1">
         <v>10000158</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" ht="20.1" customHeight="1" spans="3:6">
       <c r="C95" s="1">
         <v>91</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="E95" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" ht="20.1" customHeight="1" spans="3:6">
       <c r="C96" s="1">
         <v>92</v>
       </c>
@@ -2156,15 +2734,15 @@
         <v>24</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="97" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="97" ht="20.1" customHeight="1" spans="3:6">
       <c r="C97" s="1">
         <v>93</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E97" s="1">
         <v>30</v>
@@ -2173,12 +2751,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" ht="20.1" customHeight="1" spans="3:6">
       <c r="C98" s="1">
         <v>94</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="E98" s="1">
         <v>200000</v>
@@ -2187,12 +2765,12 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" ht="20.1" customHeight="1" spans="3:6">
       <c r="C99" s="1">
         <v>95</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E99" s="1">
         <v>120</v>
@@ -2201,34 +2779,34 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" ht="20.1" customHeight="1" spans="3:6">
       <c r="C100" s="1">
         <v>96</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="101" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="101" ht="20.1" customHeight="1" spans="3:6">
       <c r="C101" s="1">
         <v>97</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="102" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="102" ht="20.1" customHeight="1" spans="3:6">
       <c r="C102" s="1">
         <v>98</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="E102" s="1">
         <v>30000</v>
@@ -2237,12 +2815,12 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" ht="20.1" customHeight="1" spans="3:6">
       <c r="C103" s="1">
         <v>99</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E103" s="1">
         <v>61300001</v>
@@ -2251,45 +2829,45 @@
         <v>61300001</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" ht="20.1" customHeight="1" spans="3:6">
       <c r="C104" s="1">
         <v>100</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="105" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="105" ht="20.1" customHeight="1" spans="3:6">
       <c r="C105" s="1">
         <v>101</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="106" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="106" ht="20.1" customHeight="1" spans="3:6">
       <c r="C106" s="1">
         <v>102</v>
       </c>
       <c r="D106" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="E106" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="E106" s="1" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="107" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" ht="20.1" customHeight="1" spans="3:6">
       <c r="C107" s="1">
         <v>103</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="E107" s="1">
         <v>70000001</v>
@@ -2298,23 +2876,23 @@
         <v>70000001</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" ht="20.1" customHeight="1" spans="3:6">
       <c r="C108" s="1">
         <v>104</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="E108" s="1">
         <v>300</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" ht="20.1" customHeight="1" spans="3:6">
       <c r="C109" s="1">
         <v>105</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="E109" s="1">
         <v>30</v>
@@ -2323,12 +2901,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" ht="20.1" customHeight="1" spans="3:6">
       <c r="C110" s="1">
         <v>106</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="E110" s="1">
         <v>80000001</v>
@@ -2337,23 +2915,23 @@
         <v>80000001</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" ht="20.1" customHeight="1" spans="3:6">
       <c r="C111" s="1">
         <v>107</v>
       </c>
-      <c r="D111" s="10" t="s">
-        <v>148</v>
+      <c r="D111" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="112" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="112" ht="20.1" customHeight="1" spans="3:6">
       <c r="C112" s="1">
         <v>108</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="E112" s="1">
         <v>10</v>
@@ -2362,12 +2940,12 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" ht="20.1" customHeight="1" spans="3:6">
       <c r="C113" s="1">
         <v>109</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E113" s="1">
         <v>10</v>
@@ -2376,45 +2954,45 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" ht="20.1" customHeight="1" spans="3:6">
       <c r="C114" s="1">
         <v>110</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="115" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="115" ht="20.1" customHeight="1" spans="3:6">
       <c r="C115" s="1">
         <v>111</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="116" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="116" ht="20.1" customHeight="1" spans="3:6">
       <c r="C116" s="1">
         <v>112</v>
       </c>
       <c r="D116" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E116" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="117" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" ht="20.1" customHeight="1" spans="3:6">
       <c r="C117" s="1">
         <v>113</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E117" s="1">
         <v>198</v>
@@ -2423,12 +3001,12 @@
         <v>198</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" ht="20.1" customHeight="1" spans="3:6">
       <c r="C118" s="1">
         <v>114</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="E118" s="1">
         <v>90000001</v>
@@ -2437,12 +3015,12 @@
         <v>90000001</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" ht="20.1" customHeight="1" spans="3:6">
       <c r="C119" s="1">
         <v>115</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="E119" s="1">
         <v>120</v>
@@ -2451,23 +3029,23 @@
         <v>120</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" ht="20.1" customHeight="1" spans="3:6">
       <c r="C120" s="1">
         <v>116</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="121" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="121" ht="20.1" customHeight="1" spans="3:6">
       <c r="C121" s="1">
         <v>117</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E121" s="1">
         <v>6</v>
@@ -2476,12 +3054,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" ht="20.1" customHeight="1" spans="3:6">
       <c r="C122" s="1">
         <v>118</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E122" s="1">
         <v>50</v>
@@ -2490,12 +3068,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" ht="20.1" customHeight="1" spans="3:6">
       <c r="C123" s="1">
         <v>119</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E123" s="1">
         <v>60</v>
@@ -2504,14 +3082,14 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="124" ht="20.1" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E115" r:id="rId1" display="1350@602100001" xr:uid="{83D71992-AE17-4664-8460-4CE4ECA81E7C}"/>
+    <hyperlink ref="E115" r:id="rId3" display="10000131;100@601800051"/>
   </hyperlinks>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -246,7 +246,7 @@
     <t>世界等级</t>
   </si>
   <si>
-    <t>1;25@2;29@3;35@4;39@5;45@6;49@7;54@8;56@9;58@10;65@11;70</t>
+    <t>1;25@2;29@3;35@4;39@5;45@6;49@7;54@8;56@9;58@10;65@11;70@12;75</t>
   </si>
   <si>
     <t>初始制造列表</t>
@@ -1598,7 +1598,7 @@
     <col min="2" max="2" width="12.75" style="4" customWidth="1"/>
     <col min="3" max="3" width="12.625" style="1" customWidth="1"/>
     <col min="4" max="4" width="28.625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="57.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="85.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="1" customWidth="1"/>
     <col min="7" max="7" width="16.5" style="4" customWidth="1"/>
     <col min="8" max="8" width="21.5" style="4" customWidth="1"/>

--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -1,43 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA4E3FA-FAF6-464C-8822-097C77BF0654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D84" authorId="0">
+    <comment ref="D84" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>刷新概率,每天刷新上限,刷新随机列表</t>
@@ -49,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="175">
   <si>
     <t>#</t>
   </si>
@@ -568,19 +562,21 @@
   </si>
   <si>
     <t>宠物背包数量</t>
+  </si>
+  <si>
+    <t>活动活跃任务</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>700101;700201;700301;700401;700501;700601;700701;700801;700901;701001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,6 +588,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -599,172 +596,39 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -777,194 +641,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -972,253 +650,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1240,65 +676,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1585,14 +977,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="C1:H124"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="C1:H200"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="4" customWidth="1"/>
@@ -1605,13 +997,13 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="3:8">
+    <row r="1" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:8">
+    <row r="3" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1627,7 +1019,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:8">
+    <row r="4" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1641,7 +1033,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:8">
+    <row r="5" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1655,7 +1047,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
+    <row r="6" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1666,7 +1058,7 @@
         <v>30010000</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
+    <row r="7" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1677,7 +1069,7 @@
         <v>60000011</v>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:8">
+    <row r="8" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1691,7 +1083,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:8">
+    <row r="9" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1705,7 +1097,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:8">
+    <row r="10" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="7">
         <v>5</v>
       </c>
@@ -1716,7 +1108,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:8">
+    <row r="11" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1727,7 +1119,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:8">
+    <row r="12" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="7">
         <v>7</v>
       </c>
@@ -1738,7 +1130,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:8">
+    <row r="13" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="7">
         <v>8</v>
       </c>
@@ -1749,7 +1141,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="3:8">
+    <row r="14" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1760,7 +1152,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:8">
+    <row r="15" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1774,7 +1166,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="3:8">
+    <row r="16" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1785,7 +1177,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="3:6">
+    <row r="17" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1799,7 +1191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:6">
+    <row r="18" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1810,7 +1202,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:6">
+    <row r="19" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1821,7 +1213,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="3:6">
+    <row r="20" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1832,7 +1224,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="3:6">
+    <row r="21" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1843,7 +1235,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="3:6">
+    <row r="22" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -1854,7 +1246,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="3:6">
+    <row r="23" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -1865,7 +1257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="24" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -1879,7 +1271,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="3:6">
+    <row r="25" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -1890,7 +1282,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="3:6">
+    <row r="26" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -1901,7 +1293,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="27" spans="3:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -1912,7 +1304,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="28" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -1924,7 +1316,7 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="29" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -1936,7 +1328,7 @@
       </c>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="3:6">
+    <row r="30" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -1950,7 +1342,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="3:6">
+    <row r="31" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -1961,7 +1353,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" ht="20.1" customHeight="1" spans="3:6">
+    <row r="32" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1">
         <v>27</v>
       </c>
@@ -1972,7 +1364,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="3:7">
+    <row r="33" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -1983,7 +1375,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" ht="20.1" customHeight="1" spans="3:7">
+    <row r="34" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -1994,7 +1386,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="3:7">
+    <row r="35" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -2005,7 +1397,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" ht="20.1" customHeight="1" spans="3:7">
+    <row r="36" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -2016,7 +1408,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" ht="20.1" customHeight="1" spans="3:7">
+    <row r="37" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="1">
         <v>33</v>
       </c>
@@ -2027,7 +1419,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" ht="20.1" customHeight="1" spans="3:7">
+    <row r="38" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="1">
         <v>34</v>
       </c>
@@ -2038,7 +1430,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" ht="20.1" customHeight="1" spans="3:7">
+    <row r="39" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="1">
         <v>35</v>
       </c>
@@ -2049,7 +1441,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="40" ht="20.1" customHeight="1" spans="3:7">
+    <row r="40" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="1">
         <v>36</v>
       </c>
@@ -2060,7 +1452,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="41" ht="20.1" customHeight="1" spans="3:7">
+    <row r="41" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="1">
         <v>37</v>
       </c>
@@ -2071,7 +1463,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="42" ht="20.1" customHeight="1" spans="3:7">
+    <row r="42" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="1">
         <v>38</v>
       </c>
@@ -2082,7 +1474,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" ht="20.1" customHeight="1" spans="3:7">
+    <row r="43" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="1">
         <v>39</v>
       </c>
@@ -2093,7 +1485,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" ht="20.1" customHeight="1" spans="3:7">
+    <row r="44" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C44" s="1">
         <v>40</v>
       </c>
@@ -2104,7 +1496,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" ht="20.1" customHeight="1" spans="3:7">
+    <row r="45" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1">
         <v>41</v>
       </c>
@@ -2118,7 +1510,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" ht="20.1" customHeight="1" spans="3:7">
+    <row r="46" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1">
         <v>42</v>
       </c>
@@ -2129,7 +1521,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" ht="20.1" customHeight="1" spans="3:7">
+    <row r="47" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1">
         <v>43</v>
       </c>
@@ -2143,7 +1535,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" ht="20.1" customHeight="1" spans="3:7">
+    <row r="48" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1">
         <v>44</v>
       </c>
@@ -2157,7 +1549,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" ht="20.1" customHeight="1" spans="3:6">
+    <row r="49" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1">
         <v>45</v>
       </c>
@@ -2171,7 +1563,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="50" ht="20.1" customHeight="1" spans="3:6">
+    <row r="50" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="1">
         <v>46</v>
       </c>
@@ -2185,7 +1577,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="51" ht="20.1" customHeight="1" spans="3:6">
+    <row r="51" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1">
         <v>47</v>
       </c>
@@ -2199,7 +1591,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" ht="20.1" customHeight="1" spans="3:6">
+    <row r="52" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1">
         <v>48</v>
       </c>
@@ -2210,7 +1602,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" ht="20.1" customHeight="1" spans="3:6">
+    <row r="53" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="1">
         <v>49</v>
       </c>
@@ -2221,7 +1613,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" ht="20.1" customHeight="1" spans="3:6">
+    <row r="54" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C54" s="1">
         <v>50</v>
       </c>
@@ -2235,7 +1627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" ht="20.1" customHeight="1" spans="3:6">
+    <row r="55" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C55" s="1">
         <v>51</v>
       </c>
@@ -2246,7 +1638,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" ht="20.1" customHeight="1" spans="3:6">
+    <row r="56" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C56" s="1">
         <v>52</v>
       </c>
@@ -2258,7 +1650,7 @@
       </c>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" ht="20.1" customHeight="1" spans="3:6">
+    <row r="57" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C57" s="1">
         <v>53</v>
       </c>
@@ -2269,7 +1661,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" ht="20.1" customHeight="1" spans="3:6">
+    <row r="58" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="1">
         <v>54</v>
       </c>
@@ -2280,7 +1672,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" ht="20.1" customHeight="1" spans="3:6">
+    <row r="59" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="1">
         <v>55</v>
       </c>
@@ -2294,7 +1686,7 @@
         <v>20000001</v>
       </c>
     </row>
-    <row r="60" ht="20.1" customHeight="1" spans="3:6">
+    <row r="60" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C60" s="1">
         <v>56</v>
       </c>
@@ -2305,7 +1697,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" ht="20.1" customHeight="1" spans="3:6">
+    <row r="61" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C61" s="1">
         <v>57</v>
       </c>
@@ -2319,7 +1711,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" ht="20.1" customHeight="1" spans="3:6">
+    <row r="62" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="1">
         <v>58</v>
       </c>
@@ -2333,7 +1725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" ht="20.1" customHeight="1" spans="3:6">
+    <row r="63" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="1">
         <v>59</v>
       </c>
@@ -2347,7 +1739,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" ht="20.1" customHeight="1" spans="3:6">
+    <row r="64" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C64" s="1">
         <v>60</v>
       </c>
@@ -2361,7 +1753,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" ht="20.1" customHeight="1" spans="3:6">
+    <row r="65" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="1">
         <v>61</v>
       </c>
@@ -2372,7 +1764,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="66" ht="20.1" customHeight="1" spans="3:6">
+    <row r="66" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C66" s="1">
         <v>62</v>
       </c>
@@ -2383,7 +1775,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="67" ht="20.1" customHeight="1" spans="3:6">
+    <row r="67" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="1">
         <v>63</v>
       </c>
@@ -2394,7 +1786,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" ht="20.1" customHeight="1" spans="3:6">
+    <row r="68" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="1">
         <v>64</v>
       </c>
@@ -2408,7 +1800,7 @@
         <v>30000001</v>
       </c>
     </row>
-    <row r="69" ht="20.1" customHeight="1" spans="3:6">
+    <row r="69" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="1">
         <v>65</v>
       </c>
@@ -2419,7 +1811,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" ht="20.1" customHeight="1" spans="3:6">
+    <row r="70" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C70" s="1">
         <v>66</v>
       </c>
@@ -2430,7 +1822,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" ht="20.1" customHeight="1" spans="3:6">
+    <row r="71" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C71" s="1">
         <v>67</v>
       </c>
@@ -2441,7 +1833,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="72" ht="20.1" customHeight="1" spans="3:6">
+    <row r="72" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="1">
         <v>68</v>
       </c>
@@ -2452,7 +1844,7 @@
         <v>60500101</v>
       </c>
     </row>
-    <row r="73" ht="20.1" customHeight="1" spans="3:6">
+    <row r="73" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="1">
         <v>69</v>
       </c>
@@ -2463,7 +1855,7 @@
         <v>60500201</v>
       </c>
     </row>
-    <row r="74" ht="20.1" customHeight="1" spans="3:6">
+    <row r="74" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C74" s="1">
         <v>70</v>
       </c>
@@ -2474,7 +1866,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="75" ht="20.1" customHeight="1" spans="3:6">
+    <row r="75" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="1">
         <v>71</v>
       </c>
@@ -2485,7 +1877,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" ht="20.1" customHeight="1" spans="3:6">
+    <row r="76" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="1">
         <v>72</v>
       </c>
@@ -2499,7 +1891,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" ht="20.1" customHeight="1" spans="3:6">
+    <row r="77" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C77" s="1">
         <v>73</v>
       </c>
@@ -2513,7 +1905,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="78" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C78" s="1">
         <v>74</v>
       </c>
@@ -2527,7 +1919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" ht="20.1" customHeight="1" spans="3:6">
+    <row r="79" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C79" s="1">
         <v>75</v>
       </c>
@@ -2538,7 +1930,7 @@
         <v>601502001</v>
       </c>
     </row>
-    <row r="80" ht="20.1" customHeight="1" spans="3:6">
+    <row r="80" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C80" s="1">
         <v>76</v>
       </c>
@@ -2552,7 +1944,7 @@
         <v>40000001</v>
       </c>
     </row>
-    <row r="81" ht="20.1" customHeight="1" spans="3:6">
+    <row r="81" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C81" s="1">
         <v>77</v>
       </c>
@@ -2563,7 +1955,7 @@
         <v>601503011</v>
       </c>
     </row>
-    <row r="82" ht="20.1" customHeight="1" spans="3:6">
+    <row r="82" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C82" s="1">
         <v>78</v>
       </c>
@@ -2577,7 +1969,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" ht="20.1" customHeight="1" spans="3:6">
+    <row r="83" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C83" s="1">
         <v>79</v>
       </c>
@@ -2588,7 +1980,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="84" ht="20.1" customHeight="1" spans="3:6">
+    <row r="84" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C84" s="1">
         <v>80</v>
       </c>
@@ -2599,7 +1991,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="85" ht="20.1" customHeight="1" spans="3:6">
+    <row r="85" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C85" s="1">
         <v>81</v>
       </c>
@@ -2610,7 +2002,7 @@
         <v>60303101</v>
       </c>
     </row>
-    <row r="86" ht="20.1" customHeight="1" spans="3:6">
+    <row r="86" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C86" s="1">
         <v>82</v>
       </c>
@@ -2621,7 +2013,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="87" ht="20.1" customHeight="1" spans="3:6">
+    <row r="87" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C87" s="1">
         <v>83</v>
       </c>
@@ -2632,7 +2024,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="88" ht="20.1" customHeight="1" spans="3:6">
+    <row r="88" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C88" s="1">
         <v>84</v>
       </c>
@@ -2646,7 +2038,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" ht="20.1" customHeight="1" spans="3:6">
+    <row r="89" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C89" s="1">
         <v>85</v>
       </c>
@@ -2660,7 +2052,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" ht="20.1" customHeight="1" spans="3:6">
+    <row r="90" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="1">
         <v>86</v>
       </c>
@@ -2671,7 +2063,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="91" ht="20.1" customHeight="1" spans="3:6">
+    <row r="91" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C91" s="1">
         <v>87</v>
       </c>
@@ -2682,7 +2074,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="92" ht="20.1" customHeight="1" spans="3:6">
+    <row r="92" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="1">
         <v>88</v>
       </c>
@@ -2693,7 +2085,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="93" ht="20.1" customHeight="1" spans="3:6">
+    <row r="93" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="1">
         <v>89</v>
       </c>
@@ -2704,7 +2096,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="94" ht="20.1" customHeight="1" spans="3:6">
+    <row r="94" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C94" s="1">
         <v>90</v>
       </c>
@@ -2715,7 +2107,7 @@
         <v>10000158</v>
       </c>
     </row>
-    <row r="95" ht="20.1" customHeight="1" spans="3:6">
+    <row r="95" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="1">
         <v>91</v>
       </c>
@@ -2726,7 +2118,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" ht="20.1" customHeight="1" spans="3:6">
+    <row r="96" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="1">
         <v>92</v>
       </c>
@@ -2737,7 +2129,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="97" ht="20.1" customHeight="1" spans="3:6">
+    <row r="97" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="1">
         <v>93</v>
       </c>
@@ -2751,7 +2143,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" ht="20.1" customHeight="1" spans="3:6">
+    <row r="98" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="1">
         <v>94</v>
       </c>
@@ -2765,7 +2157,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="99" ht="20.1" customHeight="1" spans="3:6">
+    <row r="99" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C99" s="1">
         <v>95</v>
       </c>
@@ -2779,7 +2171,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" ht="20.1" customHeight="1" spans="3:6">
+    <row r="100" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C100" s="1">
         <v>96</v>
       </c>
@@ -2790,7 +2182,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="101" ht="20.1" customHeight="1" spans="3:6">
+    <row r="101" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C101" s="1">
         <v>97</v>
       </c>
@@ -2801,7 +2193,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="102" ht="20.1" customHeight="1" spans="3:6">
+    <row r="102" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="1">
         <v>98</v>
       </c>
@@ -2815,7 +2207,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="103" ht="20.1" customHeight="1" spans="3:6">
+    <row r="103" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C103" s="1">
         <v>99</v>
       </c>
@@ -2829,7 +2221,7 @@
         <v>61300001</v>
       </c>
     </row>
-    <row r="104" ht="20.1" customHeight="1" spans="3:6">
+    <row r="104" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C104" s="1">
         <v>100</v>
       </c>
@@ -2840,7 +2232,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="105" ht="20.1" customHeight="1" spans="3:6">
+    <row r="105" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C105" s="1">
         <v>101</v>
       </c>
@@ -2851,7 +2243,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" ht="20.1" customHeight="1" spans="3:6">
+    <row r="106" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C106" s="1">
         <v>102</v>
       </c>
@@ -2862,7 +2254,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="107" ht="20.1" customHeight="1" spans="3:6">
+    <row r="107" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C107" s="1">
         <v>103</v>
       </c>
@@ -2876,7 +2268,7 @@
         <v>70000001</v>
       </c>
     </row>
-    <row r="108" ht="20.1" customHeight="1" spans="3:6">
+    <row r="108" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C108" s="1">
         <v>104</v>
       </c>
@@ -2887,7 +2279,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="109" ht="20.1" customHeight="1" spans="3:6">
+    <row r="109" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C109" s="1">
         <v>105</v>
       </c>
@@ -2901,7 +2293,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" ht="20.1" customHeight="1" spans="3:6">
+    <row r="110" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C110" s="1">
         <v>106</v>
       </c>
@@ -2915,7 +2307,7 @@
         <v>80000001</v>
       </c>
     </row>
-    <row r="111" ht="20.1" customHeight="1" spans="3:6">
+    <row r="111" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C111" s="1">
         <v>107</v>
       </c>
@@ -2926,7 +2318,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="112" ht="20.1" customHeight="1" spans="3:6">
+    <row r="112" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C112" s="1">
         <v>108</v>
       </c>
@@ -2940,7 +2332,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" ht="20.1" customHeight="1" spans="3:6">
+    <row r="113" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="1">
         <v>109</v>
       </c>
@@ -2954,7 +2346,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" ht="20.1" customHeight="1" spans="3:6">
+    <row r="114" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C114" s="1">
         <v>110</v>
       </c>
@@ -2965,7 +2357,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="115" ht="20.1" customHeight="1" spans="3:6">
+    <row r="115" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="1">
         <v>111</v>
       </c>
@@ -2976,7 +2368,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="116" ht="20.1" customHeight="1" spans="3:6">
+    <row r="116" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="1">
         <v>112</v>
       </c>
@@ -2987,7 +2379,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="117" ht="20.1" customHeight="1" spans="3:6">
+    <row r="117" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="1">
         <v>113</v>
       </c>
@@ -3001,7 +2393,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="118" ht="20.1" customHeight="1" spans="3:6">
+    <row r="118" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="1">
         <v>114</v>
       </c>
@@ -3015,7 +2407,7 @@
         <v>90000001</v>
       </c>
     </row>
-    <row r="119" ht="20.1" customHeight="1" spans="3:6">
+    <row r="119" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C119" s="1">
         <v>115</v>
       </c>
@@ -3029,7 +2421,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="120" ht="20.1" customHeight="1" spans="3:6">
+    <row r="120" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="1">
         <v>116</v>
       </c>
@@ -3040,7 +2432,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="121" ht="20.1" customHeight="1" spans="3:6">
+    <row r="121" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C121" s="1">
         <v>117</v>
       </c>
@@ -3054,7 +2446,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" ht="20.1" customHeight="1" spans="3:6">
+    <row r="122" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="1">
         <v>118</v>
       </c>
@@ -3068,7 +2460,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="123" ht="20.1" customHeight="1" spans="3:6">
+    <row r="123" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C123" s="1">
         <v>119</v>
       </c>
@@ -3082,14 +2474,100 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" ht="20.1" customHeight="1"/>
+    <row r="124" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C124" s="1">
+        <v>120</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="125" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E115" r:id="rId3" display="10000131;100@601800051"/>
+    <hyperlink ref="E115" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -1,37 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA4E3FA-FAF6-464C-8822-097C77BF0654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D84" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D84" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>刷新概率,每天刷新上限,刷新随机列表</t>
@@ -43,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="176">
   <si>
     <t>#</t>
   </si>
@@ -565,18 +571,25 @@
   </si>
   <si>
     <t>活动活跃任务</t>
-    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>700101;700201;700301;700401;700501;700601;700701;700801;700901;701001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>家园牧场价格浮率</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,7 +601,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -596,39 +608,172 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -641,8 +786,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -650,11 +981,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -676,21 +1249,65 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -977,14 +1594,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C1:H200"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="4" customWidth="1"/>
@@ -997,13 +1614,13 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="20.1" customHeight="1"/>
+    <row r="2" ht="20.1" customHeight="1" spans="3:8">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="20.1" customHeight="1" spans="3:8">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1019,7 +1636,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="20.1" customHeight="1" spans="3:8">
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1033,7 +1650,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="20.1" customHeight="1" spans="3:8">
       <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1047,7 +1664,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1058,7 +1675,7 @@
         <v>30010000</v>
       </c>
     </row>
-    <row r="7" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1069,7 +1686,7 @@
         <v>60000011</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" ht="20.1" customHeight="1" spans="3:8">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1083,7 +1700,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" ht="20.1" customHeight="1" spans="3:8">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1097,7 +1714,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" ht="20.1" customHeight="1" spans="3:8">
       <c r="C10" s="7">
         <v>5</v>
       </c>
@@ -1108,7 +1725,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" ht="20.1" customHeight="1" spans="3:8">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1119,7 +1736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" ht="20.1" customHeight="1" spans="3:8">
       <c r="C12" s="7">
         <v>7</v>
       </c>
@@ -1130,7 +1747,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="20.1" customHeight="1" spans="3:8">
       <c r="C13" s="7">
         <v>8</v>
       </c>
@@ -1141,7 +1758,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" ht="20.1" customHeight="1" spans="3:8">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1152,7 +1769,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" ht="20.1" customHeight="1" spans="3:8">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1166,7 +1783,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" ht="20.1" customHeight="1" spans="3:8">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1177,7 +1794,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" ht="20.1" customHeight="1" spans="3:6">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1191,7 +1808,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" ht="20.1" customHeight="1" spans="3:6">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1202,7 +1819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" ht="20.1" customHeight="1" spans="3:6">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1213,7 +1830,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" ht="20.1" customHeight="1" spans="3:6">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1224,7 +1841,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" ht="20.1" customHeight="1" spans="3:6">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1235,7 +1852,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" ht="20.1" customHeight="1" spans="3:6">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -1246,7 +1863,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="23" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" ht="20.1" customHeight="1" spans="3:6">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -1257,7 +1874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -1271,7 +1888,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" ht="20.1" customHeight="1" spans="3:6">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -1282,7 +1899,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="26" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" ht="20.1" customHeight="1" spans="3:6">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -1293,7 +1910,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -1304,7 +1921,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -1316,7 +1933,7 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -1328,7 +1945,7 @@
       </c>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" ht="20.1" customHeight="1" spans="3:6">
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -1342,7 +1959,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="31" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" ht="20.1" customHeight="1" spans="3:6">
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -1353,7 +1970,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" ht="20.1" customHeight="1" spans="3:6">
       <c r="C32" s="1">
         <v>27</v>
       </c>
@@ -1364,7 +1981,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" ht="20.1" customHeight="1" spans="3:7">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -1375,7 +1992,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" ht="20.1" customHeight="1" spans="3:7">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -1386,7 +2003,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="35" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" ht="20.1" customHeight="1" spans="3:7">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -1397,7 +2014,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" ht="20.1" customHeight="1" spans="3:7">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -1408,7 +2025,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" ht="20.1" customHeight="1" spans="3:7">
       <c r="C37" s="1">
         <v>33</v>
       </c>
@@ -1419,7 +2036,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" ht="20.1" customHeight="1" spans="3:7">
       <c r="C38" s="1">
         <v>34</v>
       </c>
@@ -1430,7 +2047,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" ht="20.1" customHeight="1" spans="3:7">
       <c r="C39" s="1">
         <v>35</v>
       </c>
@@ -1441,7 +2058,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="40" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" ht="20.1" customHeight="1" spans="3:7">
       <c r="C40" s="1">
         <v>36</v>
       </c>
@@ -1452,7 +2069,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="41" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" ht="20.1" customHeight="1" spans="3:7">
       <c r="C41" s="1">
         <v>37</v>
       </c>
@@ -1463,7 +2080,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" ht="20.1" customHeight="1" spans="3:7">
       <c r="C42" s="1">
         <v>38</v>
       </c>
@@ -1474,7 +2091,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" ht="20.1" customHeight="1" spans="3:7">
       <c r="C43" s="1">
         <v>39</v>
       </c>
@@ -1485,7 +2102,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" ht="20.1" customHeight="1" spans="3:7">
       <c r="C44" s="1">
         <v>40</v>
       </c>
@@ -1496,7 +2113,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" ht="20.1" customHeight="1" spans="3:7">
       <c r="C45" s="1">
         <v>41</v>
       </c>
@@ -1510,7 +2127,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" ht="20.1" customHeight="1" spans="3:7">
       <c r="C46" s="1">
         <v>42</v>
       </c>
@@ -1521,7 +2138,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" ht="20.1" customHeight="1" spans="3:7">
       <c r="C47" s="1">
         <v>43</v>
       </c>
@@ -1535,7 +2152,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" ht="20.1" customHeight="1" spans="3:7">
       <c r="C48" s="1">
         <v>44</v>
       </c>
@@ -1549,7 +2166,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" ht="20.1" customHeight="1" spans="3:6">
       <c r="C49" s="1">
         <v>45</v>
       </c>
@@ -1563,7 +2180,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" ht="20.1" customHeight="1" spans="3:6">
       <c r="C50" s="1">
         <v>46</v>
       </c>
@@ -1577,7 +2194,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" ht="20.1" customHeight="1" spans="3:6">
       <c r="C51" s="1">
         <v>47</v>
       </c>
@@ -1591,7 +2208,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" ht="20.1" customHeight="1" spans="3:6">
       <c r="C52" s="1">
         <v>48</v>
       </c>
@@ -1602,7 +2219,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" ht="20.1" customHeight="1" spans="3:6">
       <c r="C53" s="1">
         <v>49</v>
       </c>
@@ -1613,7 +2230,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" ht="20.1" customHeight="1" spans="3:6">
       <c r="C54" s="1">
         <v>50</v>
       </c>
@@ -1627,7 +2244,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" ht="20.1" customHeight="1" spans="3:6">
       <c r="C55" s="1">
         <v>51</v>
       </c>
@@ -1638,7 +2255,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" ht="20.1" customHeight="1" spans="3:6">
       <c r="C56" s="1">
         <v>52</v>
       </c>
@@ -1650,7 +2267,7 @@
       </c>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" ht="20.1" customHeight="1" spans="3:6">
       <c r="C57" s="1">
         <v>53</v>
       </c>
@@ -1661,7 +2278,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" ht="20.1" customHeight="1" spans="3:6">
       <c r="C58" s="1">
         <v>54</v>
       </c>
@@ -1672,7 +2289,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" ht="20.1" customHeight="1" spans="3:6">
       <c r="C59" s="1">
         <v>55</v>
       </c>
@@ -1686,7 +2303,7 @@
         <v>20000001</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" ht="20.1" customHeight="1" spans="3:6">
       <c r="C60" s="1">
         <v>56</v>
       </c>
@@ -1697,7 +2314,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" ht="20.1" customHeight="1" spans="3:6">
       <c r="C61" s="1">
         <v>57</v>
       </c>
@@ -1711,7 +2328,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" ht="20.1" customHeight="1" spans="3:6">
       <c r="C62" s="1">
         <v>58</v>
       </c>
@@ -1725,7 +2342,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" ht="20.1" customHeight="1" spans="3:6">
       <c r="C63" s="1">
         <v>59</v>
       </c>
@@ -1739,7 +2356,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" ht="20.1" customHeight="1" spans="3:6">
       <c r="C64" s="1">
         <v>60</v>
       </c>
@@ -1753,7 +2370,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" ht="20.1" customHeight="1" spans="3:6">
       <c r="C65" s="1">
         <v>61</v>
       </c>
@@ -1764,7 +2381,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" ht="20.1" customHeight="1" spans="3:6">
       <c r="C66" s="1">
         <v>62</v>
       </c>
@@ -1775,7 +2392,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" ht="20.1" customHeight="1" spans="3:6">
       <c r="C67" s="1">
         <v>63</v>
       </c>
@@ -1786,7 +2403,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" ht="20.1" customHeight="1" spans="3:6">
       <c r="C68" s="1">
         <v>64</v>
       </c>
@@ -1800,7 +2417,7 @@
         <v>30000001</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" ht="20.1" customHeight="1" spans="3:6">
       <c r="C69" s="1">
         <v>65</v>
       </c>
@@ -1811,7 +2428,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" ht="20.1" customHeight="1" spans="3:6">
       <c r="C70" s="1">
         <v>66</v>
       </c>
@@ -1822,7 +2439,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" ht="20.1" customHeight="1" spans="3:6">
       <c r="C71" s="1">
         <v>67</v>
       </c>
@@ -1833,7 +2450,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" ht="20.1" customHeight="1" spans="3:6">
       <c r="C72" s="1">
         <v>68</v>
       </c>
@@ -1844,7 +2461,7 @@
         <v>60500101</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" ht="20.1" customHeight="1" spans="3:6">
       <c r="C73" s="1">
         <v>69</v>
       </c>
@@ -1855,7 +2472,7 @@
         <v>60500201</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" ht="20.1" customHeight="1" spans="3:6">
       <c r="C74" s="1">
         <v>70</v>
       </c>
@@ -1866,7 +2483,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" ht="20.1" customHeight="1" spans="3:6">
       <c r="C75" s="1">
         <v>71</v>
       </c>
@@ -1877,7 +2494,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" ht="20.1" customHeight="1" spans="3:6">
       <c r="C76" s="1">
         <v>72</v>
       </c>
@@ -1891,7 +2508,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" ht="20.1" customHeight="1" spans="3:6">
       <c r="C77" s="1">
         <v>73</v>
       </c>
@@ -1905,7 +2522,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="78" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C78" s="1">
         <v>74</v>
       </c>
@@ -1919,7 +2536,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" ht="20.1" customHeight="1" spans="3:6">
       <c r="C79" s="1">
         <v>75</v>
       </c>
@@ -1930,7 +2547,7 @@
         <v>601502001</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" ht="20.1" customHeight="1" spans="3:6">
       <c r="C80" s="1">
         <v>76</v>
       </c>
@@ -1944,7 +2561,7 @@
         <v>40000001</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" ht="20.1" customHeight="1" spans="3:6">
       <c r="C81" s="1">
         <v>77</v>
       </c>
@@ -1955,7 +2572,7 @@
         <v>601503011</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" ht="20.1" customHeight="1" spans="3:6">
       <c r="C82" s="1">
         <v>78</v>
       </c>
@@ -1969,7 +2586,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" ht="20.1" customHeight="1" spans="3:6">
       <c r="C83" s="1">
         <v>79</v>
       </c>
@@ -1980,7 +2597,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" ht="20.1" customHeight="1" spans="3:6">
       <c r="C84" s="1">
         <v>80</v>
       </c>
@@ -1991,7 +2608,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" ht="20.1" customHeight="1" spans="3:6">
       <c r="C85" s="1">
         <v>81</v>
       </c>
@@ -2002,7 +2619,7 @@
         <v>60303101</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" ht="20.1" customHeight="1" spans="3:6">
       <c r="C86" s="1">
         <v>82</v>
       </c>
@@ -2013,7 +2630,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" ht="20.1" customHeight="1" spans="3:6">
       <c r="C87" s="1">
         <v>83</v>
       </c>
@@ -2024,7 +2641,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" ht="20.1" customHeight="1" spans="3:6">
       <c r="C88" s="1">
         <v>84</v>
       </c>
@@ -2038,7 +2655,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" ht="20.1" customHeight="1" spans="3:6">
       <c r="C89" s="1">
         <v>85</v>
       </c>
@@ -2052,7 +2669,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" ht="20.1" customHeight="1" spans="3:6">
       <c r="C90" s="1">
         <v>86</v>
       </c>
@@ -2063,7 +2680,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" ht="20.1" customHeight="1" spans="3:6">
       <c r="C91" s="1">
         <v>87</v>
       </c>
@@ -2074,7 +2691,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" ht="20.1" customHeight="1" spans="3:6">
       <c r="C92" s="1">
         <v>88</v>
       </c>
@@ -2085,7 +2702,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" ht="20.1" customHeight="1" spans="3:6">
       <c r="C93" s="1">
         <v>89</v>
       </c>
@@ -2096,7 +2713,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" ht="20.1" customHeight="1" spans="3:6">
       <c r="C94" s="1">
         <v>90</v>
       </c>
@@ -2107,7 +2724,7 @@
         <v>10000158</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" ht="20.1" customHeight="1" spans="3:6">
       <c r="C95" s="1">
         <v>91</v>
       </c>
@@ -2118,7 +2735,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" ht="20.1" customHeight="1" spans="3:6">
       <c r="C96" s="1">
         <v>92</v>
       </c>
@@ -2129,7 +2746,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" ht="20.1" customHeight="1" spans="3:6">
       <c r="C97" s="1">
         <v>93</v>
       </c>
@@ -2143,7 +2760,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" ht="20.1" customHeight="1" spans="3:6">
       <c r="C98" s="1">
         <v>94</v>
       </c>
@@ -2157,7 +2774,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" ht="20.1" customHeight="1" spans="3:6">
       <c r="C99" s="1">
         <v>95</v>
       </c>
@@ -2171,7 +2788,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" ht="20.1" customHeight="1" spans="3:6">
       <c r="C100" s="1">
         <v>96</v>
       </c>
@@ -2182,7 +2799,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" ht="20.1" customHeight="1" spans="3:6">
       <c r="C101" s="1">
         <v>97</v>
       </c>
@@ -2193,7 +2810,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" ht="20.1" customHeight="1" spans="3:6">
       <c r="C102" s="1">
         <v>98</v>
       </c>
@@ -2207,7 +2824,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" ht="20.1" customHeight="1" spans="3:6">
       <c r="C103" s="1">
         <v>99</v>
       </c>
@@ -2221,7 +2838,7 @@
         <v>61300001</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" ht="20.1" customHeight="1" spans="3:6">
       <c r="C104" s="1">
         <v>100</v>
       </c>
@@ -2232,7 +2849,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" ht="20.1" customHeight="1" spans="3:6">
       <c r="C105" s="1">
         <v>101</v>
       </c>
@@ -2243,7 +2860,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" ht="20.1" customHeight="1" spans="3:6">
       <c r="C106" s="1">
         <v>102</v>
       </c>
@@ -2254,7 +2871,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" ht="20.1" customHeight="1" spans="3:6">
       <c r="C107" s="1">
         <v>103</v>
       </c>
@@ -2268,7 +2885,7 @@
         <v>70000001</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" ht="20.1" customHeight="1" spans="3:6">
       <c r="C108" s="1">
         <v>104</v>
       </c>
@@ -2279,7 +2896,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" ht="20.1" customHeight="1" spans="3:6">
       <c r="C109" s="1">
         <v>105</v>
       </c>
@@ -2293,7 +2910,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" ht="20.1" customHeight="1" spans="3:6">
       <c r="C110" s="1">
         <v>106</v>
       </c>
@@ -2307,7 +2924,7 @@
         <v>80000001</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" ht="20.1" customHeight="1" spans="3:6">
       <c r="C111" s="1">
         <v>107</v>
       </c>
@@ -2318,7 +2935,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" ht="20.1" customHeight="1" spans="3:6">
       <c r="C112" s="1">
         <v>108</v>
       </c>
@@ -2332,7 +2949,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" ht="20.1" customHeight="1" spans="3:6">
       <c r="C113" s="1">
         <v>109</v>
       </c>
@@ -2346,7 +2963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" ht="20.1" customHeight="1" spans="3:6">
       <c r="C114" s="1">
         <v>110</v>
       </c>
@@ -2357,7 +2974,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" ht="20.1" customHeight="1" spans="3:6">
       <c r="C115" s="1">
         <v>111</v>
       </c>
@@ -2368,7 +2985,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" ht="20.1" customHeight="1" spans="3:6">
       <c r="C116" s="1">
         <v>112</v>
       </c>
@@ -2379,7 +2996,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" ht="20.1" customHeight="1" spans="3:6">
       <c r="C117" s="1">
         <v>113</v>
       </c>
@@ -2393,7 +3010,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" ht="20.1" customHeight="1" spans="3:6">
       <c r="C118" s="1">
         <v>114</v>
       </c>
@@ -2407,7 +3024,7 @@
         <v>90000001</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" ht="20.1" customHeight="1" spans="3:6">
       <c r="C119" s="1">
         <v>115</v>
       </c>
@@ -2421,7 +3038,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" ht="20.1" customHeight="1" spans="3:6">
       <c r="C120" s="1">
         <v>116</v>
       </c>
@@ -2432,7 +3049,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" ht="20.1" customHeight="1" spans="3:6">
       <c r="C121" s="1">
         <v>117</v>
       </c>
@@ -2446,7 +3063,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" ht="20.1" customHeight="1" spans="3:6">
       <c r="C122" s="1">
         <v>118</v>
       </c>
@@ -2460,7 +3077,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" ht="20.1" customHeight="1" spans="3:6">
       <c r="C123" s="1">
         <v>119</v>
       </c>
@@ -2474,7 +3091,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" ht="20.1" customHeight="1" spans="3:6">
       <c r="C124" s="1">
         <v>120</v>
       </c>
@@ -2485,89 +3102,99 @@
         <v>174</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="126" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="125" ht="20.1" customHeight="1" spans="3:6">
+      <c r="C125" s="1">
+        <v>121</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E125" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="126" ht="20.1" customHeight="1"/>
+    <row r="127" ht="20.1" customHeight="1"/>
+    <row r="128" ht="20.1" customHeight="1"/>
+    <row r="129" ht="20.1" customHeight="1"/>
+    <row r="130" ht="20.1" customHeight="1"/>
+    <row r="131" ht="20.1" customHeight="1"/>
+    <row r="132" ht="20.1" customHeight="1"/>
+    <row r="133" ht="20.1" customHeight="1"/>
+    <row r="134" ht="20.1" customHeight="1"/>
+    <row r="135" ht="20.1" customHeight="1"/>
+    <row r="136" ht="20.1" customHeight="1"/>
+    <row r="137" ht="20.1" customHeight="1"/>
+    <row r="138" ht="20.1" customHeight="1"/>
+    <row r="139" ht="20.1" customHeight="1"/>
+    <row r="140" ht="20.1" customHeight="1"/>
+    <row r="141" ht="20.1" customHeight="1"/>
+    <row r="142" ht="20.1" customHeight="1"/>
+    <row r="143" ht="20.1" customHeight="1"/>
+    <row r="144" ht="20.1" customHeight="1"/>
+    <row r="145" ht="20.1" customHeight="1"/>
+    <row r="146" ht="20.1" customHeight="1"/>
+    <row r="147" ht="20.1" customHeight="1"/>
+    <row r="148" ht="20.1" customHeight="1"/>
+    <row r="149" ht="20.1" customHeight="1"/>
+    <row r="150" ht="20.1" customHeight="1"/>
+    <row r="151" ht="20.1" customHeight="1"/>
+    <row r="152" ht="20.1" customHeight="1"/>
+    <row r="153" ht="20.1" customHeight="1"/>
+    <row r="154" ht="20.1" customHeight="1"/>
+    <row r="155" ht="20.1" customHeight="1"/>
+    <row r="156" ht="20.1" customHeight="1"/>
+    <row r="157" ht="20.1" customHeight="1"/>
+    <row r="158" ht="20.1" customHeight="1"/>
+    <row r="159" ht="20.1" customHeight="1"/>
+    <row r="160" ht="20.1" customHeight="1"/>
+    <row r="161" ht="20.1" customHeight="1"/>
+    <row r="162" ht="20.1" customHeight="1"/>
+    <row r="163" ht="20.1" customHeight="1"/>
+    <row r="164" ht="20.1" customHeight="1"/>
+    <row r="165" ht="20.1" customHeight="1"/>
+    <row r="166" ht="20.1" customHeight="1"/>
+    <row r="167" ht="20.1" customHeight="1"/>
+    <row r="168" ht="20.1" customHeight="1"/>
+    <row r="169" ht="20.1" customHeight="1"/>
+    <row r="170" ht="20.1" customHeight="1"/>
+    <row r="171" ht="20.1" customHeight="1"/>
+    <row r="172" ht="20.1" customHeight="1"/>
+    <row r="173" ht="20.1" customHeight="1"/>
+    <row r="174" ht="20.1" customHeight="1"/>
+    <row r="175" ht="20.1" customHeight="1"/>
+    <row r="176" ht="20.1" customHeight="1"/>
+    <row r="177" ht="20.1" customHeight="1"/>
+    <row r="178" ht="20.1" customHeight="1"/>
+    <row r="179" ht="20.1" customHeight="1"/>
+    <row r="180" ht="20.1" customHeight="1"/>
+    <row r="181" ht="20.1" customHeight="1"/>
+    <row r="182" ht="20.1" customHeight="1"/>
+    <row r="183" ht="20.1" customHeight="1"/>
+    <row r="184" ht="20.1" customHeight="1"/>
+    <row r="185" ht="20.1" customHeight="1"/>
+    <row r="186" ht="20.1" customHeight="1"/>
+    <row r="187" ht="20.1" customHeight="1"/>
+    <row r="188" ht="20.1" customHeight="1"/>
+    <row r="189" ht="20.1" customHeight="1"/>
+    <row r="190" ht="20.1" customHeight="1"/>
+    <row r="191" ht="20.1" customHeight="1"/>
+    <row r="192" ht="20.1" customHeight="1"/>
+    <row r="193" ht="20.1" customHeight="1"/>
+    <row r="194" ht="20.1" customHeight="1"/>
+    <row r="195" ht="20.1" customHeight="1"/>
+    <row r="196" ht="20.1" customHeight="1"/>
+    <row r="197" ht="20.1" customHeight="1"/>
+    <row r="198" ht="20.1" customHeight="1"/>
+    <row r="199" ht="20.1" customHeight="1"/>
+    <row r="200" ht="20.1" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E115" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E115" r:id="rId3" display="10000131;100@601800051"/>
   </hyperlinks>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="177">
   <si>
     <t>#</t>
   </si>
@@ -576,7 +576,10 @@
     <t>700101;700201;700301;700401;700501;700601;700701;700801;700901;701001</t>
   </si>
   <si>
-    <t>家园牧场价格浮率</t>
+    <t>限时活动周任务</t>
+  </si>
+  <si>
+    <t>800101;800201;800301</t>
   </si>
 </sst>
 </file>
@@ -3109,8 +3112,8 @@
       <c r="D125" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="E125" s="1">
-        <v>1.5</v>
+      <c r="E125" s="1" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="126" ht="20.1" customHeight="1"/>

--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -579,7 +579,7 @@
     <t>限时活动周任务</t>
   </si>
   <si>
-    <t>800101;800201;800301</t>
+    <t>800101;800201;800301;800401</t>
   </si>
 </sst>
 </file>

--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -1,43 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1108565C-F0D8-4D49-88D9-2E85F56E0667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D84" authorId="0">
+    <comment ref="D84" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>刷新概率,每天刷新上限,刷新随机列表</t>
@@ -579,20 +573,15 @@
     <t>限时活动周任务</t>
   </si>
   <si>
-    <t>800101;800201;800301;800401</t>
+    <t>800101;800201;800301;800401;800501;800601;800701;800801;800901;801001</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -604,6 +593,7 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -611,172 +601,39 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -789,194 +646,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -984,253 +655,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1252,65 +681,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1597,14 +982,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="C1:H200"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="4" customWidth="1"/>
@@ -1617,13 +1002,13 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.1" customHeight="1"/>
-    <row r="2" ht="20.1" customHeight="1" spans="3:8">
+    <row r="1" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20.1" customHeight="1" spans="3:8">
+    <row r="3" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1639,7 +1024,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" ht="20.1" customHeight="1" spans="3:8">
+    <row r="4" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1653,7 +1038,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" ht="20.1" customHeight="1" spans="3:8">
+    <row r="5" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1667,7 +1052,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
+    <row r="6" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1678,7 +1063,7 @@
         <v>30010000</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
+    <row r="7" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1689,7 +1074,7 @@
         <v>60000011</v>
       </c>
     </row>
-    <row r="8" ht="20.1" customHeight="1" spans="3:8">
+    <row r="8" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1703,7 +1088,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" ht="20.1" customHeight="1" spans="3:8">
+    <row r="9" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1717,7 +1102,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" ht="20.1" customHeight="1" spans="3:8">
+    <row r="10" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C10" s="7">
         <v>5</v>
       </c>
@@ -1728,7 +1113,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" ht="20.1" customHeight="1" spans="3:8">
+    <row r="11" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1739,7 +1124,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" ht="20.1" customHeight="1" spans="3:8">
+    <row r="12" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C12" s="7">
         <v>7</v>
       </c>
@@ -1750,7 +1135,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" ht="20.1" customHeight="1" spans="3:8">
+    <row r="13" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C13" s="7">
         <v>8</v>
       </c>
@@ -1761,7 +1146,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" ht="20.1" customHeight="1" spans="3:8">
+    <row r="14" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1772,7 +1157,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" ht="20.1" customHeight="1" spans="3:8">
+    <row r="15" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1786,7 +1171,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="16" ht="20.1" customHeight="1" spans="3:8">
+    <row r="16" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1797,7 +1182,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" ht="20.1" customHeight="1" spans="3:6">
+    <row r="17" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1811,7 +1196,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" ht="20.1" customHeight="1" spans="3:6">
+    <row r="18" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1822,7 +1207,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" ht="20.1" customHeight="1" spans="3:6">
+    <row r="19" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1833,7 +1218,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" ht="20.1" customHeight="1" spans="3:6">
+    <row r="20" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1844,7 +1229,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" ht="20.1" customHeight="1" spans="3:6">
+    <row r="21" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1855,7 +1240,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" ht="20.1" customHeight="1" spans="3:6">
+    <row r="22" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -1866,7 +1251,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="23" ht="20.1" customHeight="1" spans="3:6">
+    <row r="23" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -1877,7 +1262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="24" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -1891,7 +1276,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" ht="20.1" customHeight="1" spans="3:6">
+    <row r="25" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -1902,7 +1287,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="26" ht="20.1" customHeight="1" spans="3:6">
+    <row r="26" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -1913,7 +1298,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="27" spans="3:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -1924,7 +1309,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="28" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -1936,7 +1321,7 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="29" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -1948,7 +1333,7 @@
       </c>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" ht="20.1" customHeight="1" spans="3:6">
+    <row r="30" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -1962,7 +1347,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="31" ht="20.1" customHeight="1" spans="3:6">
+    <row r="31" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -1973,7 +1358,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" ht="20.1" customHeight="1" spans="3:6">
+    <row r="32" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C32" s="1">
         <v>27</v>
       </c>
@@ -1984,7 +1369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" ht="20.1" customHeight="1" spans="3:7">
+    <row r="33" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -1995,7 +1380,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" ht="20.1" customHeight="1" spans="3:7">
+    <row r="34" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -2006,7 +1391,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="35" ht="20.1" customHeight="1" spans="3:7">
+    <row r="35" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -2017,7 +1402,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" ht="20.1" customHeight="1" spans="3:7">
+    <row r="36" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -2028,7 +1413,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" ht="20.1" customHeight="1" spans="3:7">
+    <row r="37" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C37" s="1">
         <v>33</v>
       </c>
@@ -2039,7 +1424,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" ht="20.1" customHeight="1" spans="3:7">
+    <row r="38" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C38" s="1">
         <v>34</v>
       </c>
@@ -2050,7 +1435,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" ht="20.1" customHeight="1" spans="3:7">
+    <row r="39" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C39" s="1">
         <v>35</v>
       </c>
@@ -2061,7 +1446,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="40" ht="20.1" customHeight="1" spans="3:7">
+    <row r="40" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C40" s="1">
         <v>36</v>
       </c>
@@ -2072,7 +1457,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="41" ht="20.1" customHeight="1" spans="3:7">
+    <row r="41" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C41" s="1">
         <v>37</v>
       </c>
@@ -2083,7 +1468,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="42" ht="20.1" customHeight="1" spans="3:7">
+    <row r="42" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C42" s="1">
         <v>38</v>
       </c>
@@ -2094,7 +1479,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" ht="20.1" customHeight="1" spans="3:7">
+    <row r="43" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C43" s="1">
         <v>39</v>
       </c>
@@ -2105,7 +1490,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" ht="20.1" customHeight="1" spans="3:7">
+    <row r="44" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C44" s="1">
         <v>40</v>
       </c>
@@ -2116,7 +1501,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" ht="20.1" customHeight="1" spans="3:7">
+    <row r="45" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C45" s="1">
         <v>41</v>
       </c>
@@ -2130,7 +1515,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" ht="20.1" customHeight="1" spans="3:7">
+    <row r="46" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C46" s="1">
         <v>42</v>
       </c>
@@ -2141,7 +1526,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" ht="20.1" customHeight="1" spans="3:7">
+    <row r="47" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C47" s="1">
         <v>43</v>
       </c>
@@ -2155,7 +1540,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" ht="20.1" customHeight="1" spans="3:7">
+    <row r="48" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C48" s="1">
         <v>44</v>
       </c>
@@ -2169,7 +1554,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" ht="20.1" customHeight="1" spans="3:6">
+    <row r="49" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C49" s="1">
         <v>45</v>
       </c>
@@ -2183,7 +1568,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="50" ht="20.1" customHeight="1" spans="3:6">
+    <row r="50" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C50" s="1">
         <v>46</v>
       </c>
@@ -2197,7 +1582,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="51" ht="20.1" customHeight="1" spans="3:6">
+    <row r="51" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C51" s="1">
         <v>47</v>
       </c>
@@ -2211,7 +1596,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" ht="20.1" customHeight="1" spans="3:6">
+    <row r="52" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C52" s="1">
         <v>48</v>
       </c>
@@ -2222,7 +1607,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" ht="20.1" customHeight="1" spans="3:6">
+    <row r="53" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C53" s="1">
         <v>49</v>
       </c>
@@ -2233,7 +1618,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" ht="20.1" customHeight="1" spans="3:6">
+    <row r="54" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C54" s="1">
         <v>50</v>
       </c>
@@ -2247,7 +1632,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" ht="20.1" customHeight="1" spans="3:6">
+    <row r="55" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C55" s="1">
         <v>51</v>
       </c>
@@ -2258,7 +1643,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" ht="20.1" customHeight="1" spans="3:6">
+    <row r="56" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C56" s="1">
         <v>52</v>
       </c>
@@ -2270,7 +1655,7 @@
       </c>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" ht="20.1" customHeight="1" spans="3:6">
+    <row r="57" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C57" s="1">
         <v>53</v>
       </c>
@@ -2281,7 +1666,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" ht="20.1" customHeight="1" spans="3:6">
+    <row r="58" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C58" s="1">
         <v>54</v>
       </c>
@@ -2292,7 +1677,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" ht="20.1" customHeight="1" spans="3:6">
+    <row r="59" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C59" s="1">
         <v>55</v>
       </c>
@@ -2306,7 +1691,7 @@
         <v>20000001</v>
       </c>
     </row>
-    <row r="60" ht="20.1" customHeight="1" spans="3:6">
+    <row r="60" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C60" s="1">
         <v>56</v>
       </c>
@@ -2317,7 +1702,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" ht="20.1" customHeight="1" spans="3:6">
+    <row r="61" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C61" s="1">
         <v>57</v>
       </c>
@@ -2331,7 +1716,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" ht="20.1" customHeight="1" spans="3:6">
+    <row r="62" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C62" s="1">
         <v>58</v>
       </c>
@@ -2345,7 +1730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" ht="20.1" customHeight="1" spans="3:6">
+    <row r="63" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C63" s="1">
         <v>59</v>
       </c>
@@ -2359,7 +1744,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" ht="20.1" customHeight="1" spans="3:6">
+    <row r="64" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C64" s="1">
         <v>60</v>
       </c>
@@ -2373,7 +1758,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" ht="20.1" customHeight="1" spans="3:6">
+    <row r="65" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C65" s="1">
         <v>61</v>
       </c>
@@ -2384,7 +1769,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="66" ht="20.1" customHeight="1" spans="3:6">
+    <row r="66" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C66" s="1">
         <v>62</v>
       </c>
@@ -2395,7 +1780,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="67" ht="20.1" customHeight="1" spans="3:6">
+    <row r="67" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="1">
         <v>63</v>
       </c>
@@ -2406,7 +1791,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" ht="20.1" customHeight="1" spans="3:6">
+    <row r="68" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C68" s="1">
         <v>64</v>
       </c>
@@ -2420,7 +1805,7 @@
         <v>30000001</v>
       </c>
     </row>
-    <row r="69" ht="20.1" customHeight="1" spans="3:6">
+    <row r="69" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C69" s="1">
         <v>65</v>
       </c>
@@ -2431,7 +1816,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" ht="20.1" customHeight="1" spans="3:6">
+    <row r="70" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C70" s="1">
         <v>66</v>
       </c>
@@ -2442,7 +1827,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" ht="20.1" customHeight="1" spans="3:6">
+    <row r="71" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C71" s="1">
         <v>67</v>
       </c>
@@ -2453,7 +1838,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="72" ht="20.1" customHeight="1" spans="3:6">
+    <row r="72" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C72" s="1">
         <v>68</v>
       </c>
@@ -2464,7 +1849,7 @@
         <v>60500101</v>
       </c>
     </row>
-    <row r="73" ht="20.1" customHeight="1" spans="3:6">
+    <row r="73" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C73" s="1">
         <v>69</v>
       </c>
@@ -2475,7 +1860,7 @@
         <v>60500201</v>
       </c>
     </row>
-    <row r="74" ht="20.1" customHeight="1" spans="3:6">
+    <row r="74" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C74" s="1">
         <v>70</v>
       </c>
@@ -2486,7 +1871,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="75" ht="20.1" customHeight="1" spans="3:6">
+    <row r="75" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C75" s="1">
         <v>71</v>
       </c>
@@ -2497,7 +1882,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" ht="20.1" customHeight="1" spans="3:6">
+    <row r="76" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C76" s="1">
         <v>72</v>
       </c>
@@ -2511,7 +1896,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" ht="20.1" customHeight="1" spans="3:6">
+    <row r="77" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C77" s="1">
         <v>73</v>
       </c>
@@ -2525,7 +1910,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
+    <row r="78" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C78" s="1">
         <v>74</v>
       </c>
@@ -2539,7 +1924,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" ht="20.1" customHeight="1" spans="3:6">
+    <row r="79" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C79" s="1">
         <v>75</v>
       </c>
@@ -2550,7 +1935,7 @@
         <v>601502001</v>
       </c>
     </row>
-    <row r="80" ht="20.1" customHeight="1" spans="3:6">
+    <row r="80" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C80" s="1">
         <v>76</v>
       </c>
@@ -2564,7 +1949,7 @@
         <v>40000001</v>
       </c>
     </row>
-    <row r="81" ht="20.1" customHeight="1" spans="3:6">
+    <row r="81" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C81" s="1">
         <v>77</v>
       </c>
@@ -2575,7 +1960,7 @@
         <v>601503011</v>
       </c>
     </row>
-    <row r="82" ht="20.1" customHeight="1" spans="3:6">
+    <row r="82" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C82" s="1">
         <v>78</v>
       </c>
@@ -2589,7 +1974,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" ht="20.1" customHeight="1" spans="3:6">
+    <row r="83" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C83" s="1">
         <v>79</v>
       </c>
@@ -2600,7 +1985,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="84" ht="20.1" customHeight="1" spans="3:6">
+    <row r="84" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C84" s="1">
         <v>80</v>
       </c>
@@ -2611,7 +1996,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="85" ht="20.1" customHeight="1" spans="3:6">
+    <row r="85" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C85" s="1">
         <v>81</v>
       </c>
@@ -2622,7 +2007,7 @@
         <v>60303101</v>
       </c>
     </row>
-    <row r="86" ht="20.1" customHeight="1" spans="3:6">
+    <row r="86" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C86" s="1">
         <v>82</v>
       </c>
@@ -2633,7 +2018,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="87" ht="20.1" customHeight="1" spans="3:6">
+    <row r="87" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C87" s="1">
         <v>83</v>
       </c>
@@ -2644,7 +2029,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="88" ht="20.1" customHeight="1" spans="3:6">
+    <row r="88" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C88" s="1">
         <v>84</v>
       </c>
@@ -2658,7 +2043,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" ht="20.1" customHeight="1" spans="3:6">
+    <row r="89" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C89" s="1">
         <v>85</v>
       </c>
@@ -2672,7 +2057,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" ht="20.1" customHeight="1" spans="3:6">
+    <row r="90" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C90" s="1">
         <v>86</v>
       </c>
@@ -2683,7 +2068,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="91" ht="20.1" customHeight="1" spans="3:6">
+    <row r="91" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C91" s="1">
         <v>87</v>
       </c>
@@ -2694,7 +2079,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="92" ht="20.1" customHeight="1" spans="3:6">
+    <row r="92" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C92" s="1">
         <v>88</v>
       </c>
@@ -2705,7 +2090,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="93" ht="20.1" customHeight="1" spans="3:6">
+    <row r="93" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C93" s="1">
         <v>89</v>
       </c>
@@ -2716,7 +2101,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="94" ht="20.1" customHeight="1" spans="3:6">
+    <row r="94" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C94" s="1">
         <v>90</v>
       </c>
@@ -2727,7 +2112,7 @@
         <v>10000158</v>
       </c>
     </row>
-    <row r="95" ht="20.1" customHeight="1" spans="3:6">
+    <row r="95" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C95" s="1">
         <v>91</v>
       </c>
@@ -2738,7 +2123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" ht="20.1" customHeight="1" spans="3:6">
+    <row r="96" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C96" s="1">
         <v>92</v>
       </c>
@@ -2749,7 +2134,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="97" ht="20.1" customHeight="1" spans="3:6">
+    <row r="97" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C97" s="1">
         <v>93</v>
       </c>
@@ -2763,7 +2148,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" ht="20.1" customHeight="1" spans="3:6">
+    <row r="98" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C98" s="1">
         <v>94</v>
       </c>
@@ -2777,7 +2162,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="99" ht="20.1" customHeight="1" spans="3:6">
+    <row r="99" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C99" s="1">
         <v>95</v>
       </c>
@@ -2791,7 +2176,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" ht="20.1" customHeight="1" spans="3:6">
+    <row r="100" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C100" s="1">
         <v>96</v>
       </c>
@@ -2802,7 +2187,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="101" ht="20.1" customHeight="1" spans="3:6">
+    <row r="101" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C101" s="1">
         <v>97</v>
       </c>
@@ -2813,7 +2198,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="102" ht="20.1" customHeight="1" spans="3:6">
+    <row r="102" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C102" s="1">
         <v>98</v>
       </c>
@@ -2827,7 +2212,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="103" ht="20.1" customHeight="1" spans="3:6">
+    <row r="103" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C103" s="1">
         <v>99</v>
       </c>
@@ -2841,7 +2226,7 @@
         <v>61300001</v>
       </c>
     </row>
-    <row r="104" ht="20.1" customHeight="1" spans="3:6">
+    <row r="104" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C104" s="1">
         <v>100</v>
       </c>
@@ -2852,7 +2237,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="105" ht="20.1" customHeight="1" spans="3:6">
+    <row r="105" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C105" s="1">
         <v>101</v>
       </c>
@@ -2863,7 +2248,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" ht="20.1" customHeight="1" spans="3:6">
+    <row r="106" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C106" s="1">
         <v>102</v>
       </c>
@@ -2874,7 +2259,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="107" ht="20.1" customHeight="1" spans="3:6">
+    <row r="107" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C107" s="1">
         <v>103</v>
       </c>
@@ -2888,7 +2273,7 @@
         <v>70000001</v>
       </c>
     </row>
-    <row r="108" ht="20.1" customHeight="1" spans="3:6">
+    <row r="108" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C108" s="1">
         <v>104</v>
       </c>
@@ -2899,7 +2284,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="109" ht="20.1" customHeight="1" spans="3:6">
+    <row r="109" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C109" s="1">
         <v>105</v>
       </c>
@@ -2913,7 +2298,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" ht="20.1" customHeight="1" spans="3:6">
+    <row r="110" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C110" s="1">
         <v>106</v>
       </c>
@@ -2927,7 +2312,7 @@
         <v>80000001</v>
       </c>
     </row>
-    <row r="111" ht="20.1" customHeight="1" spans="3:6">
+    <row r="111" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C111" s="1">
         <v>107</v>
       </c>
@@ -2938,7 +2323,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="112" ht="20.1" customHeight="1" spans="3:6">
+    <row r="112" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C112" s="1">
         <v>108</v>
       </c>
@@ -2952,7 +2337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" ht="20.1" customHeight="1" spans="3:6">
+    <row r="113" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C113" s="1">
         <v>109</v>
       </c>
@@ -2966,7 +2351,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" ht="20.1" customHeight="1" spans="3:6">
+    <row r="114" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C114" s="1">
         <v>110</v>
       </c>
@@ -2977,7 +2362,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="115" ht="20.1" customHeight="1" spans="3:6">
+    <row r="115" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C115" s="1">
         <v>111</v>
       </c>
@@ -2988,7 +2373,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="116" ht="20.1" customHeight="1" spans="3:6">
+    <row r="116" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C116" s="1">
         <v>112</v>
       </c>
@@ -2999,7 +2384,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="117" ht="20.1" customHeight="1" spans="3:6">
+    <row r="117" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C117" s="1">
         <v>113</v>
       </c>
@@ -3013,7 +2398,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="118" ht="20.1" customHeight="1" spans="3:6">
+    <row r="118" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C118" s="1">
         <v>114</v>
       </c>
@@ -3027,7 +2412,7 @@
         <v>90000001</v>
       </c>
     </row>
-    <row r="119" ht="20.1" customHeight="1" spans="3:6">
+    <row r="119" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C119" s="1">
         <v>115</v>
       </c>
@@ -3041,7 +2426,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="120" ht="20.1" customHeight="1" spans="3:6">
+    <row r="120" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C120" s="1">
         <v>116</v>
       </c>
@@ -3052,7 +2437,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="121" ht="20.1" customHeight="1" spans="3:6">
+    <row r="121" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C121" s="1">
         <v>117</v>
       </c>
@@ -3066,7 +2451,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" ht="20.1" customHeight="1" spans="3:6">
+    <row r="122" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C122" s="1">
         <v>118</v>
       </c>
@@ -3080,7 +2465,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="123" ht="20.1" customHeight="1" spans="3:6">
+    <row r="123" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C123" s="1">
         <v>119</v>
       </c>
@@ -3094,7 +2479,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" ht="20.1" customHeight="1" spans="3:6">
+    <row r="124" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C124" s="1">
         <v>120</v>
       </c>
@@ -3105,7 +2490,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="125" ht="20.1" customHeight="1" spans="3:6">
+    <row r="125" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C125" s="1">
         <v>121</v>
       </c>
@@ -3116,88 +2501,88 @@
         <v>176</v>
       </c>
     </row>
-    <row r="126" ht="20.1" customHeight="1"/>
-    <row r="127" ht="20.1" customHeight="1"/>
-    <row r="128" ht="20.1" customHeight="1"/>
-    <row r="129" ht="20.1" customHeight="1"/>
-    <row r="130" ht="20.1" customHeight="1"/>
-    <row r="131" ht="20.1" customHeight="1"/>
-    <row r="132" ht="20.1" customHeight="1"/>
-    <row r="133" ht="20.1" customHeight="1"/>
-    <row r="134" ht="20.1" customHeight="1"/>
-    <row r="135" ht="20.1" customHeight="1"/>
-    <row r="136" ht="20.1" customHeight="1"/>
-    <row r="137" ht="20.1" customHeight="1"/>
-    <row r="138" ht="20.1" customHeight="1"/>
-    <row r="139" ht="20.1" customHeight="1"/>
-    <row r="140" ht="20.1" customHeight="1"/>
-    <row r="141" ht="20.1" customHeight="1"/>
-    <row r="142" ht="20.1" customHeight="1"/>
-    <row r="143" ht="20.1" customHeight="1"/>
-    <row r="144" ht="20.1" customHeight="1"/>
-    <row r="145" ht="20.1" customHeight="1"/>
-    <row r="146" ht="20.1" customHeight="1"/>
-    <row r="147" ht="20.1" customHeight="1"/>
-    <row r="148" ht="20.1" customHeight="1"/>
-    <row r="149" ht="20.1" customHeight="1"/>
-    <row r="150" ht="20.1" customHeight="1"/>
-    <row r="151" ht="20.1" customHeight="1"/>
-    <row r="152" ht="20.1" customHeight="1"/>
-    <row r="153" ht="20.1" customHeight="1"/>
-    <row r="154" ht="20.1" customHeight="1"/>
-    <row r="155" ht="20.1" customHeight="1"/>
-    <row r="156" ht="20.1" customHeight="1"/>
-    <row r="157" ht="20.1" customHeight="1"/>
-    <row r="158" ht="20.1" customHeight="1"/>
-    <row r="159" ht="20.1" customHeight="1"/>
-    <row r="160" ht="20.1" customHeight="1"/>
-    <row r="161" ht="20.1" customHeight="1"/>
-    <row r="162" ht="20.1" customHeight="1"/>
-    <row r="163" ht="20.1" customHeight="1"/>
-    <row r="164" ht="20.1" customHeight="1"/>
-    <row r="165" ht="20.1" customHeight="1"/>
-    <row r="166" ht="20.1" customHeight="1"/>
-    <row r="167" ht="20.1" customHeight="1"/>
-    <row r="168" ht="20.1" customHeight="1"/>
-    <row r="169" ht="20.1" customHeight="1"/>
-    <row r="170" ht="20.1" customHeight="1"/>
-    <row r="171" ht="20.1" customHeight="1"/>
-    <row r="172" ht="20.1" customHeight="1"/>
-    <row r="173" ht="20.1" customHeight="1"/>
-    <row r="174" ht="20.1" customHeight="1"/>
-    <row r="175" ht="20.1" customHeight="1"/>
-    <row r="176" ht="20.1" customHeight="1"/>
-    <row r="177" ht="20.1" customHeight="1"/>
-    <row r="178" ht="20.1" customHeight="1"/>
-    <row r="179" ht="20.1" customHeight="1"/>
-    <row r="180" ht="20.1" customHeight="1"/>
-    <row r="181" ht="20.1" customHeight="1"/>
-    <row r="182" ht="20.1" customHeight="1"/>
-    <row r="183" ht="20.1" customHeight="1"/>
-    <row r="184" ht="20.1" customHeight="1"/>
-    <row r="185" ht="20.1" customHeight="1"/>
-    <row r="186" ht="20.1" customHeight="1"/>
-    <row r="187" ht="20.1" customHeight="1"/>
-    <row r="188" ht="20.1" customHeight="1"/>
-    <row r="189" ht="20.1" customHeight="1"/>
-    <row r="190" ht="20.1" customHeight="1"/>
-    <row r="191" ht="20.1" customHeight="1"/>
-    <row r="192" ht="20.1" customHeight="1"/>
-    <row r="193" ht="20.1" customHeight="1"/>
-    <row r="194" ht="20.1" customHeight="1"/>
-    <row r="195" ht="20.1" customHeight="1"/>
-    <row r="196" ht="20.1" customHeight="1"/>
-    <row r="197" ht="20.1" customHeight="1"/>
-    <row r="198" ht="20.1" customHeight="1"/>
-    <row r="199" ht="20.1" customHeight="1"/>
-    <row r="200" ht="20.1" customHeight="1"/>
+    <row r="126" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="127" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="128" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E115" r:id="rId3" display="10000131;100@601800051"/>
+    <hyperlink ref="E115" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
-  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/GlobalValueConfig.xlsx
+++ b/Excel/GlobalValueConfig.xlsx
@@ -1,37 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1108565C-F0D8-4D49-88D9-2E85F56E0667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="GlobalValueProto" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
   </authors>
   <commentList>
-    <comment ref="D84" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D84" authorId="0">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>刷新概率,每天刷新上限,刷新随机列表</t>
@@ -43,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="178">
   <si>
     <t>#</t>
   </si>
@@ -574,14 +580,22 @@
   </si>
   <si>
     <t>800101;800201;800301;800401;800501;800601;800701;800801;800901;801001</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>家园商店倍率</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -593,7 +607,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
@@ -601,39 +614,172 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -646,8 +792,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -655,11 +987,253 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -681,21 +1255,65 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -982,14 +1600,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="C1:H200"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="21.125" style="4" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="4" customWidth="1"/>
@@ -1002,13 +1620,13 @@
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" ht="20.1" customHeight="1"/>
+    <row r="2" ht="20.1" customHeight="1" spans="3:8">
       <c r="D2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="20.1" customHeight="1" spans="3:8">
       <c r="C3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1024,7 +1642,7 @@
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
     </row>
-    <row r="4" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" ht="20.1" customHeight="1" spans="3:8">
       <c r="C4" s="5" t="s">
         <v>1</v>
       </c>
@@ -1038,7 +1656,7 @@
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
     </row>
-    <row r="5" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" ht="20.1" customHeight="1" spans="3:8">
       <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1052,7 +1670,7 @@
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
     </row>
-    <row r="6" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1063,7 +1681,7 @@
         <v>30010000</v>
       </c>
     </row>
-    <row r="7" spans="3:8" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:8">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1074,7 +1692,7 @@
         <v>60000011</v>
       </c>
     </row>
-    <row r="8" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" ht="20.1" customHeight="1" spans="3:8">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1088,7 +1706,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="9" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" ht="20.1" customHeight="1" spans="3:8">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1102,7 +1720,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" ht="20.1" customHeight="1" spans="3:8">
       <c r="C10" s="7">
         <v>5</v>
       </c>
@@ -1113,7 +1731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" ht="20.1" customHeight="1" spans="3:8">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1124,7 +1742,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" ht="20.1" customHeight="1" spans="3:8">
       <c r="C12" s="7">
         <v>7</v>
       </c>
@@ -1135,7 +1753,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" ht="20.1" customHeight="1" spans="3:8">
       <c r="C13" s="7">
         <v>8</v>
       </c>
@@ -1146,7 +1764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" ht="20.1" customHeight="1" spans="3:8">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1157,7 +1775,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" ht="20.1" customHeight="1" spans="3:8">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1171,7 +1789,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="16" spans="3:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" ht="20.1" customHeight="1" spans="3:8">
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1182,7 +1800,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" ht="20.1" customHeight="1" spans="3:6">
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1196,7 +1814,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" ht="20.1" customHeight="1" spans="3:6">
       <c r="C18" s="1">
         <v>13</v>
       </c>
@@ -1207,7 +1825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" ht="20.1" customHeight="1" spans="3:6">
       <c r="C19" s="1">
         <v>14</v>
       </c>
@@ -1218,7 +1836,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" ht="20.1" customHeight="1" spans="3:6">
       <c r="C20" s="1">
         <v>15</v>
       </c>
@@ -1229,7 +1847,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" ht="20.1" customHeight="1" spans="3:6">
       <c r="C21" s="1">
         <v>16</v>
       </c>
@@ -1240,7 +1858,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" ht="20.1" customHeight="1" spans="3:6">
       <c r="C22" s="1">
         <v>17</v>
       </c>
@@ -1251,7 +1869,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="23" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" ht="20.1" customHeight="1" spans="3:6">
       <c r="C23" s="1">
         <v>18</v>
       </c>
@@ -1262,7 +1880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C24" s="1">
         <v>19</v>
       </c>
@@ -1276,7 +1894,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" ht="20.1" customHeight="1" spans="3:6">
       <c r="C25" s="1">
         <v>20</v>
       </c>
@@ -1287,7 +1905,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="26" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" ht="20.1" customHeight="1" spans="3:6">
       <c r="C26" s="1">
         <v>21</v>
       </c>
@@ -1298,7 +1916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="3:6" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" s="1" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C27" s="1">
         <v>22</v>
       </c>
@@ -1309,7 +1927,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="28" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C28" s="1">
         <v>23</v>
       </c>
@@ -1321,7 +1939,7 @@
       </c>
       <c r="F28" s="1"/>
     </row>
-    <row r="29" spans="3:6" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" s="3" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C29" s="1">
         <v>24</v>
       </c>
@@ -1333,7 +1951,7 @@
       </c>
       <c r="F29" s="1"/>
     </row>
-    <row r="30" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" ht="20.1" customHeight="1" spans="3:6">
       <c r="C30" s="1">
         <v>25</v>
       </c>
@@ -1347,7 +1965,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="31" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" ht="20.1" customHeight="1" spans="3:6">
       <c r="C31" s="1">
         <v>26</v>
       </c>
@@ -1358,7 +1976,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="32" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" ht="20.1" customHeight="1" spans="3:6">
       <c r="C32" s="1">
         <v>27</v>
       </c>
@@ -1369,7 +1987,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" ht="20.1" customHeight="1" spans="3:7">
       <c r="C33" s="1">
         <v>28</v>
       </c>
@@ -1380,7 +1998,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="34" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" ht="20.1" customHeight="1" spans="3:7">
       <c r="C34" s="1">
         <v>29</v>
       </c>
@@ -1391,7 +2009,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="35" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" ht="20.1" customHeight="1" spans="3:7">
       <c r="C35" s="1">
         <v>30</v>
       </c>
@@ -1402,7 +2020,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" ht="20.1" customHeight="1" spans="3:7">
       <c r="C36" s="1">
         <v>31</v>
       </c>
@@ -1413,7 +2031,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="37" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" ht="20.1" customHeight="1" spans="3:7">
       <c r="C37" s="1">
         <v>33</v>
       </c>
@@ -1424,7 +2042,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" ht="20.1" customHeight="1" spans="3:7">
       <c r="C38" s="1">
         <v>34</v>
       </c>
@@ -1435,7 +2053,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" ht="20.1" customHeight="1" spans="3:7">
       <c r="C39" s="1">
         <v>35</v>
       </c>
@@ -1446,7 +2064,7 @@
         <v>86400</v>
       </c>
     </row>
-    <row r="40" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" ht="20.1" customHeight="1" spans="3:7">
       <c r="C40" s="1">
         <v>36</v>
       </c>
@@ -1457,7 +2075,7 @@
         <v>259200</v>
       </c>
     </row>
-    <row r="41" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" ht="20.1" customHeight="1" spans="3:7">
       <c r="C41" s="1">
         <v>37</v>
       </c>
@@ -1468,7 +2086,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="42" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" ht="20.1" customHeight="1" spans="3:7">
       <c r="C42" s="1">
         <v>38</v>
       </c>
@@ -1479,7 +2097,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="43" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" ht="20.1" customHeight="1" spans="3:7">
       <c r="C43" s="1">
         <v>39</v>
       </c>
@@ -1490,7 +2108,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="44" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" ht="20.1" customHeight="1" spans="3:7">
       <c r="C44" s="1">
         <v>40</v>
       </c>
@@ -1501,7 +2119,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" ht="20.1" customHeight="1" spans="3:7">
       <c r="C45" s="1">
         <v>41</v>
       </c>
@@ -1515,7 +2133,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="46" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" ht="20.1" customHeight="1" spans="3:7">
       <c r="C46" s="1">
         <v>42</v>
       </c>
@@ -1526,7 +2144,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="47" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" ht="20.1" customHeight="1" spans="3:7">
       <c r="C47" s="1">
         <v>43</v>
       </c>
@@ -1540,7 +2158,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="48" spans="3:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" ht="20.1" customHeight="1" spans="3:7">
       <c r="C48" s="1">
         <v>44</v>
       </c>
@@ -1554,7 +2172,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" ht="20.1" customHeight="1" spans="3:6">
       <c r="C49" s="1">
         <v>45</v>
       </c>
@@ -1568,7 +2186,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="50" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" ht="20.1" customHeight="1" spans="3:6">
       <c r="C50" s="1">
         <v>46</v>
       </c>
@@ -1582,7 +2200,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="51" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" ht="20.1" customHeight="1" spans="3:6">
       <c r="C51" s="1">
         <v>47</v>
       </c>
@@ -1596,7 +2214,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="52" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" ht="20.1" customHeight="1" spans="3:6">
       <c r="C52" s="1">
         <v>48</v>
       </c>
@@ -1607,7 +2225,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="53" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" ht="20.1" customHeight="1" spans="3:6">
       <c r="C53" s="1">
         <v>49</v>
       </c>
@@ -1618,7 +2236,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="54" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" ht="20.1" customHeight="1" spans="3:6">
       <c r="C54" s="1">
         <v>50</v>
       </c>
@@ -1632,7 +2250,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" ht="20.1" customHeight="1" spans="3:6">
       <c r="C55" s="1">
         <v>51</v>
       </c>
@@ -1643,7 +2261,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="56" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" ht="20.1" customHeight="1" spans="3:6">
       <c r="C56" s="1">
         <v>52</v>
       </c>
@@ -1655,7 +2273,7 @@
       </c>
       <c r="F56" s="4"/>
     </row>
-    <row r="57" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" ht="20.1" customHeight="1" spans="3:6">
       <c r="C57" s="1">
         <v>53</v>
       </c>
@@ -1666,7 +2284,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" ht="20.1" customHeight="1" spans="3:6">
       <c r="C58" s="1">
         <v>54</v>
       </c>
@@ -1677,7 +2295,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="59" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" ht="20.1" customHeight="1" spans="3:6">
       <c r="C59" s="1">
         <v>55</v>
       </c>
@@ -1691,7 +2309,7 @@
         <v>20000001</v>
       </c>
     </row>
-    <row r="60" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" ht="20.1" customHeight="1" spans="3:6">
       <c r="C60" s="1">
         <v>56</v>
       </c>
@@ -1702,7 +2320,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="61" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" ht="20.1" customHeight="1" spans="3:6">
       <c r="C61" s="1">
         <v>57</v>
       </c>
@@ -1716,7 +2334,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="62" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" ht="20.1" customHeight="1" spans="3:6">
       <c r="C62" s="1">
         <v>58</v>
       </c>
@@ -1730,7 +2348,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" ht="20.1" customHeight="1" spans="3:6">
       <c r="C63" s="1">
         <v>59</v>
       </c>
@@ -1744,7 +2362,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="64" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" ht="20.1" customHeight="1" spans="3:6">
       <c r="C64" s="1">
         <v>60</v>
       </c>
@@ -1758,7 +2376,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="65" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" ht="20.1" customHeight="1" spans="3:6">
       <c r="C65" s="1">
         <v>61</v>
       </c>
@@ -1769,7 +2387,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="66" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" ht="20.1" customHeight="1" spans="3:6">
       <c r="C66" s="1">
         <v>62</v>
       </c>
@@ -1780,7 +2398,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="67" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" ht="20.1" customHeight="1" spans="3:6">
       <c r="C67" s="1">
         <v>63</v>
       </c>
@@ -1791,7 +2409,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="68" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" ht="20.1" customHeight="1" spans="3:6">
       <c r="C68" s="1">
         <v>64</v>
       </c>
@@ -1805,7 +2423,7 @@
         <v>30000001</v>
       </c>
     </row>
-    <row r="69" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" ht="20.1" customHeight="1" spans="3:6">
       <c r="C69" s="1">
         <v>65</v>
       </c>
@@ -1816,7 +2434,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="70" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" ht="20.1" customHeight="1" spans="3:6">
       <c r="C70" s="1">
         <v>66</v>
       </c>
@@ -1827,7 +2445,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" ht="20.1" customHeight="1" spans="3:6">
       <c r="C71" s="1">
         <v>67</v>
       </c>
@@ -1838,7 +2456,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="72" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" ht="20.1" customHeight="1" spans="3:6">
       <c r="C72" s="1">
         <v>68</v>
       </c>
@@ -1849,7 +2467,7 @@
         <v>60500101</v>
       </c>
     </row>
-    <row r="73" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" ht="20.1" customHeight="1" spans="3:6">
       <c r="C73" s="1">
         <v>69</v>
       </c>
@@ -1860,7 +2478,7 @@
         <v>60500201</v>
       </c>
     </row>
-    <row r="74" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" ht="20.1" customHeight="1" spans="3:6">
       <c r="C74" s="1">
         <v>70</v>
       </c>
@@ -1871,7 +2489,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" ht="20.1" customHeight="1" spans="3:6">
       <c r="C75" s="1">
         <v>71</v>
       </c>
@@ -1882,7 +2500,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" ht="20.1" customHeight="1" spans="3:6">
       <c r="C76" s="1">
         <v>72</v>
       </c>
@@ -1896,7 +2514,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="77" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" ht="20.1" customHeight="1" spans="3:6">
       <c r="C77" s="1">
         <v>73</v>
       </c>
@@ -1910,7 +2528,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="78" spans="3:6" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" s="2" customFormat="1" ht="20.1" customHeight="1" spans="3:6">
       <c r="C78" s="1">
         <v>74</v>
       </c>
@@ -1924,7 +2542,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" ht="20.1" customHeight="1" spans="3:6">
       <c r="C79" s="1">
         <v>75</v>
       </c>
@@ -1935,7 +2553,7 @@
         <v>601502001</v>
       </c>
     </row>
-    <row r="80" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" ht="20.1" customHeight="1" spans="3:6">
       <c r="C80" s="1">
         <v>76</v>
       </c>
@@ -1949,7 +2567,7 @@
         <v>40000001</v>
       </c>
     </row>
-    <row r="81" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" ht="20.1" customHeight="1" spans="3:6">
       <c r="C81" s="1">
         <v>77</v>
       </c>
@@ -1960,7 +2578,7 @@
         <v>601503011</v>
       </c>
     </row>
-    <row r="82" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" ht="20.1" customHeight="1" spans="3:6">
       <c r="C82" s="1">
         <v>78</v>
       </c>
@@ -1974,7 +2592,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="83" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" ht="20.1" customHeight="1" spans="3:6">
       <c r="C83" s="1">
         <v>79</v>
       </c>
@@ -1985,7 +2603,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="84" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" ht="20.1" customHeight="1" spans="3:6">
       <c r="C84" s="1">
         <v>80</v>
       </c>
@@ -1996,7 +2614,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="85" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" ht="20.1" customHeight="1" spans="3:6">
       <c r="C85" s="1">
         <v>81</v>
       </c>
@@ -2007,7 +2625,7 @@
         <v>60303101</v>
       </c>
     </row>
-    <row r="86" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" ht="20.1" customHeight="1" spans="3:6">
       <c r="C86" s="1">
         <v>82</v>
       </c>
@@ -2018,7 +2636,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="87" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" ht="20.1" customHeight="1" spans="3:6">
       <c r="C87" s="1">
         <v>83</v>
       </c>
@@ -2029,7 +2647,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="88" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" ht="20.1" customHeight="1" spans="3:6">
       <c r="C88" s="1">
         <v>84</v>
       </c>
@@ -2043,7 +2661,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="89" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" ht="20.1" customHeight="1" spans="3:6">
       <c r="C89" s="1">
         <v>85</v>
       </c>
@@ -2057,7 +2675,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" ht="20.1" customHeight="1" spans="3:6">
       <c r="C90" s="1">
         <v>86</v>
       </c>
@@ -2068,7 +2686,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="91" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" ht="20.1" customHeight="1" spans="3:6">
       <c r="C91" s="1">
         <v>87</v>
       </c>
@@ -2079,7 +2697,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="92" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" ht="20.1" customHeight="1" spans="3:6">
       <c r="C92" s="1">
         <v>88</v>
       </c>
@@ -2090,7 +2708,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="93" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" ht="20.1" customHeight="1" spans="3:6">
       <c r="C93" s="1">
         <v>89</v>
       </c>
@@ -2101,7 +2719,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="94" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" ht="20.1" customHeight="1" spans="3:6">
       <c r="C94" s="1">
         <v>90</v>
       </c>
@@ -2112,7 +2730,7 @@
         <v>10000158</v>
       </c>
     </row>
-    <row r="95" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" ht="20.1" customHeight="1" spans="3:6">
       <c r="C95" s="1">
         <v>91</v>
       </c>
@@ -2123,7 +2741,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="96" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" ht="20.1" customHeight="1" spans="3:6">
       <c r="C96" s="1">
         <v>92</v>
       </c>
@@ -2134,7 +2752,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="97" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" ht="20.1" customHeight="1" spans="3:6">
       <c r="C97" s="1">
         <v>93</v>
       </c>
@@ -2148,7 +2766,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="98" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" ht="20.1" customHeight="1" spans="3:6">
       <c r="C98" s="1">
         <v>94</v>
       </c>
@@ -2162,7 +2780,7 @@
         <v>200000</v>
       </c>
     </row>
-    <row r="99" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" ht="20.1" customHeight="1" spans="3:6">
       <c r="C99" s="1">
         <v>95</v>
       </c>
@@ -2176,7 +2794,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="100" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" ht="20.1" customHeight="1" spans="3:6">
       <c r="C100" s="1">
         <v>96</v>
       </c>
@@ -2187,7 +2805,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="101" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" ht="20.1" customHeight="1" spans="3:6">
       <c r="C101" s="1">
         <v>97</v>
       </c>
@@ -2198,7 +2816,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="102" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" ht="20.1" customHeight="1" spans="3:6">
       <c r="C102" s="1">
         <v>98</v>
       </c>
@@ -2212,7 +2830,7 @@
         <v>50000</v>
       </c>
     </row>
-    <row r="103" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" ht="20.1" customHeight="1" spans="3:6">
       <c r="C103" s="1">
         <v>99</v>
       </c>
@@ -2226,7 +2844,7 @@
         <v>61300001</v>
       </c>
     </row>
-    <row r="104" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" ht="20.1" customHeight="1" spans="3:6">
       <c r="C104" s="1">
         <v>100</v>
       </c>
@@ -2237,7 +2855,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="105" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" ht="20.1" customHeight="1" spans="3:6">
       <c r="C105" s="1">
         <v>101</v>
       </c>
@@ -2248,7 +2866,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="106" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" ht="20.1" customHeight="1" spans="3:6">
       <c r="C106" s="1">
         <v>102</v>
       </c>
@@ -2259,7 +2877,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="107" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" ht="20.1" customHeight="1" spans="3:6">
       <c r="C107" s="1">
         <v>103</v>
       </c>
@@ -2273,7 +2891,7 @@
         <v>70000001</v>
       </c>
     </row>
-    <row r="108" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" ht="20.1" customHeight="1" spans="3:6">
       <c r="C108" s="1">
         <v>104</v>
       </c>
@@ -2284,7 +2902,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="109" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" ht="20.1" customHeight="1" spans="3:6">
       <c r="C109" s="1">
         <v>105</v>
       </c>
@@ -2298,7 +2916,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="110" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" ht="20.1" customHeight="1" spans="3:6">
       <c r="C110" s="1">
         <v>106</v>
       </c>
@@ -2312,7 +2930,7 @@
         <v>80000001</v>
       </c>
     </row>
-    <row r="111" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" ht="20.1" customHeight="1" spans="3:6">
       <c r="C111" s="1">
         <v>107</v>
       </c>
@@ -2323,7 +2941,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="112" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" ht="20.1" customHeight="1" spans="3:6">
       <c r="C112" s="1">
         <v>108</v>
       </c>
@@ -2337,7 +2955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="113" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" ht="20.1" customHeight="1" spans="3:6">
       <c r="C113" s="1">
         <v>109</v>
       </c>
@@ -2351,7 +2969,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" ht="20.1" customHeight="1" spans="3:6">
       <c r="C114" s="1">
         <v>110</v>
       </c>
@@ -2362,7 +2980,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="115" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" ht="20.1" customHeight="1" spans="3:6">
       <c r="C115" s="1">
         <v>111</v>
       </c>
@@ -2373,7 +2991,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="116" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" ht="20.1" customHeight="1" spans="3:6">
       <c r="C116" s="1">
         <v>112</v>
       </c>
@@ -2384,7 +3002,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="117" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" ht="20.1" customHeight="1" spans="3:6">
       <c r="C117" s="1">
         <v>113</v>
       </c>
@@ -2398,7 +3016,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="118" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" ht="20.1" customHeight="1" spans="3:6">
       <c r="C118" s="1">
         <v>114</v>
       </c>
@@ -2412,7 +3030,7 @@
         <v>90000001</v>
       </c>
     </row>
-    <row r="119" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" ht="20.1" customHeight="1" spans="3:6">
       <c r="C119" s="1">
         <v>115</v>
       </c>
@@ -2426,7 +3044,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="120" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" ht="20.1" customHeight="1" spans="3:6">
       <c r="C120" s="1">
         <v>116</v>
       </c>
@@ -2437,7 +3055,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="121" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" ht="20.1" customHeight="1" spans="3:6">
       <c r="C121" s="1">
         <v>117</v>
       </c>
@@ -2451,7 +3069,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" ht="20.1" customHeight="1" spans="3:6">
       <c r="C122" s="1">
         <v>118</v>
       </c>
@@ -2465,7 +3083,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="123" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" ht="20.1" customHeight="1" spans="3:6">
       <c r="C123" s="1">
         <v>119</v>
       </c>
@@ -2479,7 +3097,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="124" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" ht="20.1" customHeight="1" spans="3:6">
       <c r="C124" s="1">
         <v>120</v>
       </c>
@@ -2490,7 +3108,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="125" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" ht="20.1" customHeight="1" spans="3:6">
       <c r="C125" s="1">
         <v>121</v>
       </c>
@@ -2501,88 +3119,98 @@
         <v>176</v>
       </c>
     </row>
-    <row r="126" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="127" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="128" spans="3:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="129" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="130" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="131" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="132" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="133" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="134" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="135" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="136" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="137" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="138" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="139" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="140" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="141" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="142" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="143" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="144" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="145" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="146" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="147" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="148" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="149" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="150" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="151" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="152" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="153" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="154" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="155" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="156" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="157" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="158" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="159" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="160" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="161" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="162" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="163" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="164" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="165" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="166" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="167" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="168" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="169" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="170" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="171" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="172" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="173" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="174" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="175" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="176" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="190" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="191" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="192" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="199" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="200" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="126" ht="20.1" customHeight="1" spans="3:6">
+      <c r="C126" s="1">
+        <v>122</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E126" s="1">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="127" ht="20.1" customHeight="1"/>
+    <row r="128" ht="20.1" customHeight="1"/>
+    <row r="129" ht="20.1" customHeight="1"/>
+    <row r="130" ht="20.1" customHeight="1"/>
+    <row r="131" ht="20.1" customHeight="1"/>
+    <row r="132" ht="20.1" customHeight="1"/>
+    <row r="133" ht="20.1" customHeight="1"/>
+    <row r="134" ht="20.1" customHeight="1"/>
+    <row r="135" ht="20.1" customHeight="1"/>
+    <row r="136" ht="20.1" customHeight="1"/>
+    <row r="137" ht="20.1" customHeight="1"/>
+    <row r="138" ht="20.1" customHeight="1"/>
+    <row r="139" ht="20.1" customHeight="1"/>
+    <row r="140" ht="20.1" customHeight="1"/>
+    <row r="141" ht="20.1" customHeight="1"/>
+    <row r="142" ht="20.1" customHeight="1"/>
+    <row r="143" ht="20.1" customHeight="1"/>
+    <row r="144" ht="20.1" customHeight="1"/>
+    <row r="145" ht="20.1" customHeight="1"/>
+    <row r="146" ht="20.1" customHeight="1"/>
+    <row r="147" ht="20.1" customHeight="1"/>
+    <row r="148" ht="20.1" customHeight="1"/>
+    <row r="149" ht="20.1" customHeight="1"/>
+    <row r="150" ht="20.1" customHeight="1"/>
+    <row r="151" ht="20.1" customHeight="1"/>
+    <row r="152" ht="20.1" customHeight="1"/>
+    <row r="153" ht="20.1" customHeight="1"/>
+    <row r="154" ht="20.1" customHeight="1"/>
+    <row r="155" ht="20.1" customHeight="1"/>
+    <row r="156" ht="20.1" customHeight="1"/>
+    <row r="157" ht="20.1" customHeight="1"/>
+    <row r="158" ht="20.1" customHeight="1"/>
+    <row r="159" ht="20.1" customHeight="1"/>
+    <row r="160" ht="20.1" customHeight="1"/>
+    <row r="161" ht="20.1" customHeight="1"/>
+    <row r="162" ht="20.1" customHeight="1"/>
+    <row r="163" ht="20.1" customHeight="1"/>
+    <row r="164" ht="20.1" customHeight="1"/>
+    <row r="165" ht="20.1" customHeight="1"/>
+    <row r="166" ht="20.1" customHeight="1"/>
+    <row r="167" ht="20.1" customHeight="1"/>
+    <row r="168" ht="20.1" customHeight="1"/>
+    <row r="169" ht="20.1" customHeight="1"/>
+    <row r="170" ht="20.1" customHeight="1"/>
+    <row r="171" ht="20.1" customHeight="1"/>
+    <row r="172" ht="20.1" customHeight="1"/>
+    <row r="173" ht="20.1" customHeight="1"/>
+    <row r="174" ht="20.1" customHeight="1"/>
+    <row r="175" ht="20.1" customHeight="1"/>
+    <row r="176" ht="20.1" customHeight="1"/>
+    <row r="177" ht="20.1" customHeight="1"/>
+    <row r="178" ht="20.1" customHeight="1"/>
+    <row r="179" ht="20.1" customHeight="1"/>
+    <row r="180" ht="20.1" customHeight="1"/>
+    <row r="181" ht="20.1" customHeight="1"/>
+    <row r="182" ht="20.1" customHeight="1"/>
+    <row r="183" ht="20.1" customHeight="1"/>
+    <row r="184" ht="20.1" customHeight="1"/>
+    <row r="185" ht="20.1" customHeight="1"/>
+    <row r="186" ht="20.1" customHeight="1"/>
+    <row r="187" ht="20.1" customHeight="1"/>
+    <row r="188" ht="20.1" customHeight="1"/>
+    <row r="189" ht="20.1" customHeight="1"/>
+    <row r="190" ht="20.1" customHeight="1"/>
+    <row r="191" ht="20.1" customHeight="1"/>
+    <row r="192" ht="20.1" customHeight="1"/>
+    <row r="193" ht="20.1" customHeight="1"/>
+    <row r="194" ht="20.1" customHeight="1"/>
+    <row r="195" ht="20.1" customHeight="1"/>
+    <row r="196" ht="20.1" customHeight="1"/>
+    <row r="197" ht="20.1" customHeight="1"/>
+    <row r="198" ht="20.1" customHeight="1"/>
+    <row r="199" ht="20.1" customHeight="1"/>
+    <row r="200" ht="20.1" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E115" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="E115" r:id="rId3" display="10000131;100@601800051"/>
   </hyperlinks>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>